--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370211759094161</v>
+        <v>8.370209922089437</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367994289859086</v>
+        <v>8.367995840274627</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394466094669992</v>
+        <v>8.394462968798496</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.41074789984399</v>
+        <v>8.410746376732117</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.42419977529689</v>
+        <v>8.424199858737415</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428449171866275</v>
+        <v>8.42845066268208</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.42724147713797</v>
+        <v>8.427244364186846</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.4317132819093</v>
+        <v>8.43171786622176</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429883365803498</v>
+        <v>8.429898506656835</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439876234701282</v>
+        <v>8.439892762380158</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446406212844577</v>
+        <v>8.446424070520234</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439542728188901</v>
+        <v>8.439560436850046</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419376881741638</v>
+        <v>8.41939595674901</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.40176488142232</v>
+        <v>8.401790277883808</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373900916292643</v>
+        <v>8.373923192964078</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336287579928953</v>
+        <v>8.336312008407294</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281070237092141</v>
+        <v>8.281104132355468</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226643879983207</v>
+        <v>8.226680337582188</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173651667473912</v>
+        <v>8.173671169650421</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130528017180785</v>
+        <v>8.130540217066102</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133198136076789</v>
+        <v>8.133194737587736</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185485506648959</v>
+        <v>8.185469397745257</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216633612127801</v>
+        <v>8.216583662329443</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200666129518915</v>
+        <v>8.200602767317822</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171934432757498</v>
+        <v>8.171865630617878</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127367362494006</v>
+        <v>8.127302524713993</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104413892719414</v>
+        <v>8.104360701749851</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115273108994234</v>
+        <v>8.115232411226916</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164069909426368</v>
+        <v>8.164068900519631</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192412589412148</v>
+        <v>8.192423671892735</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173356035643216</v>
+        <v>8.173379630454109</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198061874798018</v>
+        <v>8.198121502009315</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.201525196241157</v>
+        <v>8.201641974277397</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.233072248585632</v>
+        <v>8.233209804451853</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.323960067280964</v>
+        <v>8.324142263456332</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.281913355510632</v>
+        <v>8.282013852218924</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.283801963066988</v>
+        <v>8.283940815741968</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.267270806909574</v>
+        <v>8.267403906285002</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.278108653492964</v>
+        <v>8.278263216836656</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.31334947418882</v>
+        <v>8.313546465368116</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.334321023450741</v>
+        <v>8.334537593320455</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.241323124395636</v>
+        <v>8.241546559237996</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.151005858757919</v>
+        <v>8.151198696261675</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.057701564368237</v>
+        <v>8.057827547463377</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.013287495250754</v>
+        <v>8.013395059172701</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968417767158018</v>
+        <v>7.968472446399586</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942585438718147</v>
+        <v>7.942621988152686</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.948650616270564</v>
+        <v>7.948725498065723</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915404442800027</v>
+        <v>7.915438450103213</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887905811210508</v>
+        <v>7.887920981045531</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872902189740233</v>
+        <v>7.872928542978832</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.893726672845056</v>
+        <v>7.89380891219114</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.866284289607039</v>
+        <v>7.866402861833227</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.813141347488124</v>
+        <v>7.813283630229283</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.772677795197401</v>
+        <v>7.772822000377468</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.752129033813987</v>
+        <v>7.752230417486971</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.74994728664961</v>
+        <v>7.749968299736662</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751673854955223</v>
+        <v>7.751625974643941</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.75515667984401</v>
+        <v>7.755010770626601</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.747217602650189</v>
+        <v>7.746960343630413</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.740923315343876</v>
+        <v>7.742110312869129</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.722566112719235</v>
+        <v>7.724083334756502</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.71581553416179</v>
+        <v>7.717707323390425</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.715385730257207</v>
+        <v>7.718175874539211</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.716462107000027</v>
+        <v>7.720264739319424</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.71886188848033</v>
+        <v>7.723600636312342</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.724718790793547</v>
+        <v>7.730331708442551</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.752121484572724</v>
+        <v>7.75880653270882</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.807519892741813</v>
+        <v>7.815197666620598</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.834455563759761</v>
+        <v>7.840886522245434</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.865291878348388</v>
+        <v>7.874032570314274</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.916667635664852</v>
+        <v>7.927173058884694</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.93677500318608</v>
+        <v>7.951968857022091</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.990860532889023</v>
+        <v>8.012281542718902</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B115"/>
+  <dimension ref="A1:B116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370209922089437</v>
+        <v>8.370208123754164</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367995840274627</v>
+        <v>8.367997357678325</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394462968798496</v>
+        <v>8.394459909353877</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410746376732117</v>
+        <v>8.410744886163336</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424199858737415</v>
+        <v>8.424199940782216</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.42845066268208</v>
+        <v>8.428452122389322</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427244364186846</v>
+        <v>8.427247190588549</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.43171786622176</v>
+        <v>8.431722353858028</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429898506656835</v>
+        <v>8.429913326844815</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439892762380158</v>
+        <v>8.439908941562457</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446424070520234</v>
+        <v>8.446441551733482</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439560436850046</v>
+        <v>8.439577772149381</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.41939595674901</v>
+        <v>8.419414631551431</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401790277883808</v>
+        <v>8.401815140606136</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373923192964078</v>
+        <v>8.373945000894254</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336312008407294</v>
+        <v>8.336335927290181</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281104132355468</v>
+        <v>8.281137322651377</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226680337582188</v>
+        <v>8.226716045210175</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173671169650421</v>
+        <v>8.173690269728294</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130540217066102</v>
+        <v>8.130552166606369</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133194737587736</v>
+        <v>8.13319142597728</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185469397745257</v>
+        <v>8.185453641190566</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216583662329443</v>
+        <v>8.216534757568731</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200602767317822</v>
+        <v>8.200540719935082</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171865630617878</v>
+        <v>8.171798245885416</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127302524713993</v>
+        <v>8.127239007669411</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104360701749851</v>
+        <v>8.104308572296876</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115232411226916</v>
+        <v>8.115192496483733</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164068900519631</v>
+        <v>8.164067858320657</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192423671892735</v>
+        <v>8.192434511296891</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173379630454109</v>
+        <v>8.173402712504739</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198121502009315</v>
+        <v>8.198179910267628</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.201641974277397</v>
+        <v>8.201756395157201</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.233209804451853</v>
+        <v>8.233344579438198</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.324142263456332</v>
+        <v>8.324320739416262</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.282013852218924</v>
+        <v>8.282112212019937</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.283940815741968</v>
+        <v>8.284076723654968</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.267403906285002</v>
+        <v>8.267534133707922</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.278263216836656</v>
+        <v>8.278414454969438</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.313546465368116</v>
+        <v>8.313739243972988</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.334537593320455</v>
+        <v>8.334749566181687</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.241546559237996</v>
+        <v>8.241765335080016</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.151198696261675</v>
+        <v>8.151387558815983</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.057827547463377</v>
+        <v>8.057950993302622</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.013395059172701</v>
+        <v>8.013500478519081</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968472446399586</v>
+        <v>7.968526043460505</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942621988152686</v>
+        <v>7.942657796538435</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.948725498065723</v>
+        <v>7.948798845467024</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915438450103213</v>
+        <v>7.915471710891001</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887920981045531</v>
+        <v>7.887935744946642</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872928542978832</v>
+        <v>7.872954233992254</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.89380891219114</v>
+        <v>7.893889380373095</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.866402861833227</v>
+        <v>7.866518935822546</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.813283630229283</v>
+        <v>7.813423042327629</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.772822000377468</v>
+        <v>7.772963375976175</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.752230417486971</v>
+        <v>7.752329929467582</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749968299736662</v>
+        <v>7.749989164056835</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751625974643941</v>
+        <v>7.751579296005257</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.755010770626601</v>
+        <v>7.754868006254428</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.746960343630413</v>
+        <v>7.746708151924914</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.742110312869129</v>
+        <v>7.741800730758937</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.724083334756502</v>
+        <v>7.725906484962349</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.717707323390425</v>
+        <v>7.719580391361368</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.718175874539211</v>
+        <v>7.719650192240588</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.720264739319424</v>
+        <v>7.72057771356332</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.723600636312342</v>
+        <v>7.722859609801448</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.730331708442551</v>
+        <v>7.728319783920182</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.75880653270882</v>
+        <v>7.755066488134768</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.815197666620598</v>
+        <v>7.808829059713277</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.840886522245434</v>
+        <v>7.833064813381691</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.874032570314274</v>
+        <v>7.862216611670959</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.927173058884694</v>
+        <v>7.909042263909357</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.951968857022091</v>
+        <v>7.923657969519603</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,15 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>8.012281542718902</v>
+        <v>7.953810707521281</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B116">
+        <v>7.879298207521281</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370208123754164</v>
+        <v>8.370206362880104</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367997357678325</v>
+        <v>8.367998843113213</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394459909353877</v>
+        <v>8.394456914241532</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410744886163336</v>
+        <v>8.410743427106123</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424199940782216</v>
+        <v>8.4242000214638</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428452122389322</v>
+        <v>8.42845355195149</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427247190588549</v>
+        <v>8.427249958233951</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431722353858028</v>
+        <v>8.431726747843825</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429913326844815</v>
+        <v>8.429927836444747</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439908941562457</v>
+        <v>8.439924783153751</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446441551733482</v>
+        <v>8.446458668262583</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439577772149381</v>
+        <v>8.439594745769405</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419414631551431</v>
+        <v>8.419432918609115</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401815140606136</v>
+        <v>8.401839486234461</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373945000894254</v>
+        <v>8.373966354718448</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336335927290181</v>
+        <v>8.336359352352453</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281137322651377</v>
+        <v>8.281169829734541</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226716045210175</v>
+        <v>8.226751025747555</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173690269728294</v>
+        <v>8.17370898000561</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130552166606369</v>
+        <v>8.130563873423158</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.13319142597728</v>
+        <v>8.133188198062264</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185453641190566</v>
+        <v>8.185438225581304</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216534757568731</v>
+        <v>8.216486865419725</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200540719935082</v>
+        <v>8.200479946920483</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171798245885416</v>
+        <v>8.171732235280489</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127239007669411</v>
+        <v>8.127176771508562</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104308572296876</v>
+        <v>8.104257473031144</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115192496483733</v>
+        <v>8.115153342598617</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164067858320657</v>
+        <v>8.164066785527147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192434511296891</v>
+        <v>8.192445115462958</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173402712504739</v>
+        <v>8.173425298243066</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198179910267628</v>
+        <v>8.198237136443009</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.201756395157201</v>
+        <v>8.2018685293553</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.233344579438198</v>
+        <v>8.233476656818949</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.324320739416262</v>
+        <v>8.324495607737919</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.282112212019937</v>
+        <v>8.282208502303945</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.284076723654968</v>
+        <v>8.2842097794029</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.267534133707922</v>
+        <v>8.267661580940574</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.278414454969438</v>
+        <v>8.278562473832466</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.313739243972988</v>
+        <v>8.313927943404646</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.334749566181687</v>
+        <v>8.334957086613974</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.241765335080016</v>
+        <v>8.241979595869719</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.151387558815983</v>
+        <v>8.151572567771066</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.057950993302622</v>
+        <v>8.058071977491952</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.013500478519081</v>
+        <v>8.013603816551592</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968526043460505</v>
+        <v>7.96857859006675</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942657796538435</v>
+        <v>7.942692886193788</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.948798845467024</v>
+        <v>7.948870705127439</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915471710891001</v>
+        <v>7.915504249418044</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887935744946642</v>
+        <v>7.887950118208898</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872954233992254</v>
+        <v>7.872979286661704</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.893889380373095</v>
+        <v>7.893968133838382</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.866518935822546</v>
+        <v>7.866632589503771</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.813423042327629</v>
+        <v>7.81355966929775</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.772963375976175</v>
+        <v>7.773102003755632</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.752329929467582</v>
+        <v>7.752427620036952</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.749989164056835</v>
+        <v>7.750009875684198</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751579296005257</v>
+        <v>7.751533776695923</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.754868006254428</v>
+        <v>7.754728288292438</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.746708151924914</v>
+        <v>7.746460882751582</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.741800730758937</v>
+        <v>7.741496794103348</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.725906484962349</v>
+        <v>7.727577584924133</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.719580391361368</v>
+        <v>7.721301926528506</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.719650192240588</v>
+        <v>7.721013942560527</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.72057771356332</v>
+        <v>7.720719967810211</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.722859609801448</v>
+        <v>7.722255070165857</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.728319783920182</v>
+        <v>7.726572717728084</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.755066488134768</v>
+        <v>7.751738913101224</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.808829059713277</v>
+        <v>7.803073280619707</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.833064813381691</v>
+        <v>7.825983686823269</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.862216611670959</v>
+        <v>7.851593626810515</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.909042263909357</v>
+        <v>7.893019608116322</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.923657969519603</v>
+        <v>7.899675336960167</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.953810707521281</v>
+        <v>7.909302945407487</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.879298207521281</v>
+        <v>7.834790445407486</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370206362880104</v>
+        <v>8.370204638308822</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.367998843113213</v>
+        <v>8.368000297578849</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394456914241532</v>
+        <v>8.394453981453978</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410743427106123</v>
+        <v>8.410741998572085</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.4242000214638</v>
+        <v>8.424200100813792</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.42845355195149</v>
+        <v>8.4284549522927</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427249958233951</v>
+        <v>8.427252668936132</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431726747843825</v>
+        <v>8.431731051079941</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429927836444747</v>
+        <v>8.429942045116194</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439924783153751</v>
+        <v>8.439940297609359</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446458668262583</v>
+        <v>8.446475431399623</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439594745769405</v>
+        <v>8.439611368910347</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419432918609115</v>
+        <v>8.419450829870485</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401839486234461</v>
+        <v>8.401863330729176</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373966354718448</v>
+        <v>8.373987268469158</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336359352352453</v>
+        <v>8.336382298724754</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281169829734541</v>
+        <v>8.281201674474142</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226751025747555</v>
+        <v>8.226785301154415</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.17370898000561</v>
+        <v>8.173727312284438</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130563873423158</v>
+        <v>8.130575344832023</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133188198062264</v>
+        <v>8.133185050809647</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185438225581304</v>
+        <v>8.185423139999505</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216486865419725</v>
+        <v>8.216439954783027</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200479946920483</v>
+        <v>8.200420409463989</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171732235280489</v>
+        <v>8.171667557264707</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127176771508562</v>
+        <v>8.127115777963127</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104257473031144</v>
+        <v>8.104207373838573</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115153342598617</v>
+        <v>8.115114928224909</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164066785527147</v>
+        <v>8.164065684659214</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192445115462958</v>
+        <v>8.192455491898576</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173425298243066</v>
+        <v>8.173447403424376</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198237136443009</v>
+        <v>8.19829321593874</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.2018685293553</v>
+        <v>8.201978444572186</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.233476656818949</v>
+        <v>8.23360611658501</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.324495607737919</v>
+        <v>8.324666976510262</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.282208502303945</v>
+        <v>8.282302787659074</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.2842097794029</v>
+        <v>8.28434007174469</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.267661580940574</v>
+        <v>8.267786335885123</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.278562473832466</v>
+        <v>8.278707374922643</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.313927943404646</v>
+        <v>8.314112691502302</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.334957086613974</v>
+        <v>8.335160293206966</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.241979595869719</v>
+        <v>8.242189479696538</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.151572567771066</v>
+        <v>8.151753839599582</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.058071977491952</v>
+        <v>8.058190572674597</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.013603816551592</v>
+        <v>8.013705134077988</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.96857859006675</v>
+        <v>7.968630116719597</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942692886193788</v>
+        <v>7.94272727854946</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.948870705127439</v>
+        <v>7.948941121828828</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915504249418044</v>
+        <v>7.915536088901967</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887950118208898</v>
+        <v>7.887964115393177</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.872979286661704</v>
+        <v>7.873003723759336</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.893968133838382</v>
+        <v>7.894045226667353</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.866632589503771</v>
+        <v>7.86674389760602</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.81355966929775</v>
+        <v>7.813693593311509</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.773102003755632</v>
+        <v>7.773237962387406</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.752427620036952</v>
+        <v>7.752523537738329</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750009875684198</v>
+        <v>7.750030431180727</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751533776695923</v>
+        <v>7.751489376264655</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.754728288292438</v>
+        <v>7.75459152228979</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.746460882751582</v>
+        <v>7.7462183966486</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.741496794103348</v>
+        <v>7.741198355883108</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.727577584924133</v>
+        <v>7.729371984814337</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.721301926528506</v>
+        <v>7.72319363054204</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.721013942560527</v>
+        <v>7.722534322236656</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.720719967810211</v>
+        <v>7.721540268189199</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.722255070165857</v>
+        <v>7.722157514334373</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.726572717728084</v>
+        <v>7.725487204348394</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.751738913101224</v>
+        <v>7.749272843952346</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.803073280619707</v>
+        <v>7.798443227403993</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.825983686823269</v>
+        <v>7.820219489754683</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.851593626810515</v>
+        <v>7.842842905070346</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.893019608116322</v>
+        <v>7.879848536200521</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.899675336960167</v>
+        <v>7.880631038312572</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.909302945407487</v>
+        <v>7.876851769557518</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.834790445407486</v>
+        <v>7.567848182002564</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370204638308822</v>
+        <v>8.370202948929172</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368000297578849</v>
+        <v>8.368001722033556</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394453981453978</v>
+        <v>8.394451109066384</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410741998572085</v>
+        <v>8.410740599613707</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424200100813792</v>
+        <v>8.424200178862941</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.4284549522927</v>
+        <v>8.428456324299679</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427252668936132</v>
+        <v>8.427255324434348</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431731051079941</v>
+        <v>8.431735266348602</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429942045116194</v>
+        <v>8.429955962122362</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439940297609359</v>
+        <v>8.439955494957333</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446475431399623</v>
+        <v>8.446491851975319</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439611368910347</v>
+        <v>8.439627652314771</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419450829870485</v>
+        <v>8.419468376798179</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401863330729176</v>
+        <v>8.401886689400733</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.373987268469158</v>
+        <v>8.374007755606813</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336382298724754</v>
+        <v>8.336404780926092</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281201674474142</v>
+        <v>8.281232876898439</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226785301154415</v>
+        <v>8.226818892516285</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173727312284438</v>
+        <v>8.173745277895573</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130575344832023</v>
+        <v>8.130586587857678</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133185050809647</v>
+        <v>8.13318198132791</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185423139999505</v>
+        <v>8.185408373987297</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216439954783027</v>
+        <v>8.216393995818681</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200420409463989</v>
+        <v>8.200362070313563</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171667557264707</v>
+        <v>8.171604171954364</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127115777963127</v>
+        <v>8.127055990270488</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104207373838573</v>
+        <v>8.104158245762267</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115114928224909</v>
+        <v>8.115077232798352</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164065684659214</v>
+        <v>8.16406455807172</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192455491898576</v>
+        <v>8.192465647797821</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173447403424376</v>
+        <v>8.173469043147213</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19829321593874</v>
+        <v>8.198348182763279</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.201978444572186</v>
+        <v>8.202086205868891</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.23360611658501</v>
+        <v>8.233733035603702</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.324666976510262</v>
+        <v>8.324834949555045</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.282302787659074</v>
+        <v>8.282395130015331</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.28434007174469</v>
+        <v>8.2844676857979</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.267786335885123</v>
+        <v>8.267908482784119</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.278707374922643</v>
+        <v>8.278849255522802</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.314112691502302</v>
+        <v>8.314293610829445</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.335160293206966</v>
+        <v>8.33535931886693</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.242189479696538</v>
+        <v>8.242395119085788</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.151753839599582</v>
+        <v>8.151931486138633</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.058190572674597</v>
+        <v>8.05830684867415</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.013705134077988</v>
+        <v>8.013804489569402</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968630116719597</v>
+        <v>7.968680652753985</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.94272727854946</v>
+        <v>7.942760994192199</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.948941121828828</v>
+        <v>7.949010138574735</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915536088901967</v>
+        <v>7.915567251578095</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887964115393177</v>
+        <v>7.887977750368695</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873003723759336</v>
+        <v>7.873027567010794</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894045226667353</v>
+        <v>7.894120710695719</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.86674389760602</v>
+        <v>7.866852931820882</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.813693593311509</v>
+        <v>7.813824893358731</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.773237962387406</v>
+        <v>7.773371327595664</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.752523537738329</v>
+        <v>7.7526177294489</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750030431180727</v>
+        <v>7.750050827556324</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751489376264655</v>
+        <v>7.751446056050741</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.75459152228979</v>
+        <v>7.754457617584199</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.7462183966486</v>
+        <v>7.745980559239765</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.741198355883108</v>
+        <v>7.740905273882833</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.729371984814337</v>
+        <v>7.73090392577816</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.72319363054204</v>
+        <v>7.724786939681275</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.722534322236656</v>
+        <v>7.723796622669021</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.721540268189199</v>
+        <v>7.721675648564876</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.722157514334373</v>
+        <v>7.721654734558571</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.725487204348394</v>
+        <v>7.723959176394814</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.749272843952346</v>
+        <v>7.746344249935392</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.798443227403993</v>
+        <v>7.793400269844882</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.820219489754683</v>
+        <v>7.814068443186731</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.842842905070346</v>
+        <v>7.83380709615659</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.879848536200521</v>
+        <v>7.866701955865148</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.880631038312572</v>
+        <v>7.862244572170896</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.876851769557518</v>
+        <v>7.847737186232083</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.567848182002564</v>
+        <v>7.566393081351285</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370202948929172</v>
+        <v>8.370201293674889</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368001722033556</v>
+        <v>8.36800311739653</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394451109066384</v>
+        <v>8.394448295232349</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410740599613707</v>
+        <v>8.410739229322292</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424200178862941</v>
+        <v>8.424200255641162</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428456324299679</v>
+        <v>8.428457668823654</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427255324434348</v>
+        <v>8.427257926397754</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431735266348602</v>
+        <v>8.431739396319474</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429955962122362</v>
+        <v>8.429969596350238</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439955494957333</v>
+        <v>8.439970384820073</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446491851975319</v>
+        <v>8.446507940382356</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439627652314771</v>
+        <v>8.439643606290732</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419468376798179</v>
+        <v>8.419485570393483</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401886689400733</v>
+        <v>8.401909576942398</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374007755606813</v>
+        <v>8.374027829048631</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336404780926092</v>
+        <v>8.336426812894402</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281232876898439</v>
+        <v>8.28126345623669</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226818892516285</v>
+        <v>8.226851820087216</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173745277895573</v>
+        <v>8.173762887721814</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130586587857678</v>
+        <v>8.130597609248309</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.13318198132791</v>
+        <v>8.133178986859036</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185408373987297</v>
+        <v>8.185393917522983</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216393995818681</v>
+        <v>8.216348959883112</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200362070313563</v>
+        <v>8.200304893697844</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171604171954364</v>
+        <v>8.17154204103899</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.127055990270488</v>
+        <v>8.126997373100593</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104158245762267</v>
+        <v>8.104110060947738</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115077232798352</v>
+        <v>8.115040236502033</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.16406455807172</v>
+        <v>8.164063407965688</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192465647797821</v>
+        <v>8.192475590057281</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173469043147213</v>
+        <v>8.173490231887076</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198348182763279</v>
+        <v>8.198402069598044</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.202086205868891</v>
+        <v>8.202191875794052</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.233733035603702</v>
+        <v>8.233857487769351</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.324834949555045</v>
+        <v>8.324999626634966</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.282395130015331</v>
+        <v>8.282485588779871</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.2844676857979</v>
+        <v>8.284592703223373</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.267908482784119</v>
+        <v>8.268028102408632</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.278849255522802</v>
+        <v>8.278988208917793</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.314293610829445</v>
+        <v>8.314470818942707</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.33535931886693</v>
+        <v>8.335554291104685</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.242395119085788</v>
+        <v>8.242596641275632</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.151931486138633</v>
+        <v>8.152105614817529</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.05830684867415</v>
+        <v>8.058420872629496</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.013804489569402</v>
+        <v>8.013901939271047</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968680652753985</v>
+        <v>7.968730226393586</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942760994192199</v>
+        <v>7.94279405290595</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949010138574735</v>
+        <v>7.949077796677747</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915567251578095</v>
+        <v>7.915597758750715</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.887977750368695</v>
+        <v>7.88799103635264</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873027567010794</v>
+        <v>7.873050837153645</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894120710695719</v>
+        <v>7.894194635629539</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.866852931820882</v>
+        <v>7.86695976095483</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.813824893358731</v>
+        <v>7.813953645398792</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.773371327595664</v>
+        <v>7.773502172292521</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.7526177294489</v>
+        <v>7.752710240448292</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750050827556324</v>
+        <v>7.750071062232028</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751446056050741</v>
+        <v>7.751403779088946</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.754457617584199</v>
+        <v>7.754326487117456</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.745980559239765</v>
+        <v>7.7457472410116</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.740905273882833</v>
+        <v>7.740617410510479</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.73090392577816</v>
+        <v>7.731932680165816</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.724786939681275</v>
+        <v>7.725805466565813</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.723796622669021</v>
+        <v>7.724566816222195</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.721675648564876</v>
+        <v>7.722028813121574</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.721654734558571</v>
+        <v>7.721688987659706</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.723959176394814</v>
+        <v>7.723608856153447</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.746344249935392</v>
+        <v>7.74531710434993</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.793400269844882</v>
+        <v>7.791083290460787</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.814068443186731</v>
+        <v>7.811447705398811</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.83380709615659</v>
+        <v>7.831007591488255</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.866701955865148</v>
+        <v>7.862571636479578</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.862244572170896</v>
+        <v>7.857410969842267</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.847737186232083</v>
+        <v>7.842305538520215</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.566393081351285</v>
+        <v>7.613074407673768</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370201293674889</v>
+        <v>8.370199671522345</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.36800311739653</v>
+        <v>8.368004484549814</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394448295232349</v>
+        <v>8.394445538179951</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410739229322292</v>
+        <v>8.410737886825959</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424200255641162</v>
+        <v>8.42420033117754</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428457668823654</v>
+        <v>8.428458986682077</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427257926397754</v>
+        <v>8.427260476428875</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431739396319474</v>
+        <v>8.431743443555291</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429969596350238</v>
+        <v>8.429982956329489</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439970384820073</v>
+        <v>8.439984976434623</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446507940382356</v>
+        <v>8.446523706597301</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439643606290732</v>
+        <v>8.439659240733505</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419485570393483</v>
+        <v>8.419502421219297</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401909576942398</v>
+        <v>8.401932007461012</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374027829048631</v>
+        <v>8.374047501195726</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336426812894402</v>
+        <v>8.336448408015332</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.28126345623669</v>
+        <v>8.281293430958559</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226851820087216</v>
+        <v>8.226884103330299</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173762887721814</v>
+        <v>8.173780152219848</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130597609248309</v>
+        <v>8.130608415489021</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133178986859036</v>
+        <v>8.133176064771019</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185393917522983</v>
+        <v>8.185379760998575</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216348959883112</v>
+        <v>8.216304819469821</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200304893697844</v>
+        <v>8.200248845253428</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.17154204103899</v>
+        <v>8.171481127704689</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126997373100593</v>
+        <v>8.126939892487023</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104110060947738</v>
+        <v>8.104062792591172</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115040236502033</v>
+        <v>8.115003920233168</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164063407965688</v>
+        <v>8.164062236398816</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192475590057281</v>
+        <v>8.192485325291168</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173490231887076</v>
+        <v>8.173510983528109</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198402069598044</v>
+        <v>8.198454907861262</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.202191875794052</v>
+        <v>8.202295514503676</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.233857487769351</v>
+        <v>8.233979544145274</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.324999626634966</v>
+        <v>8.325161103649714</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.282485588779871</v>
+        <v>8.282574220964081</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.284592703223373</v>
+        <v>8.284715202398781</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.268028102408632</v>
+        <v>8.268145272234905</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.278988208917793</v>
+        <v>8.279124324597383</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.314470818942707</v>
+        <v>8.314644428644435</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.335554291104685</v>
+        <v>8.335745332306209</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.242596641275632</v>
+        <v>8.242794168477657</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.152105614817529</v>
+        <v>8.152276328872309</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.058420872629496</v>
+        <v>8.058532709122129</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.013901939271047</v>
+        <v>8.013997537306711</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968730226393586</v>
+        <v>7.968778864802783</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.94279405290595</v>
+        <v>7.942826473710628</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949077796677747</v>
+        <v>7.949144135841742</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915597758750715</v>
+        <v>7.915627630841225</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.88799103635264</v>
+        <v>7.888003985947191</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873050837153645</v>
+        <v>7.873073553991983</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894194635629539</v>
+        <v>7.894267049153208</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.86695976095483</v>
+        <v>7.867064451072565</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.813953645398792</v>
+        <v>7.814079922503673</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.773502172292521</v>
+        <v>7.77363056670608</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.752710240448292</v>
+        <v>7.752801114483841</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750071062232028</v>
+        <v>7.75009113300624</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751403779088946</v>
+        <v>7.751362510020253</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.754326487117456</v>
+        <v>7.754198047261426</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.7457472410116</v>
+        <v>7.745518317101702</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.740617410510479</v>
+        <v>7.740334632623949</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.731932680165816</v>
+        <v>7.732923247049637</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.725805466565813</v>
+        <v>7.726796991768918</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.724566816222195</v>
+        <v>7.725316478576298</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.722028813121574</v>
+        <v>7.722386279734992</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.721688987659706</v>
+        <v>7.72174161988803</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.723608856153447</v>
+        <v>7.723294940638078</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.74531710434993</v>
+        <v>7.74436009383705</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.791083290460787</v>
+        <v>7.788909990202254</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.811447705398811</v>
+        <v>7.808994104813785</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.831007591488255</v>
+        <v>7.828404101522892</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.862571636479578</v>
+        <v>7.85878175886609</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.857410969842267</v>
+        <v>7.853087203124709</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.842305538520215</v>
+        <v>7.837695456818896</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.613074407673768</v>
+        <v>7.644097351911792</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370199671522345</v>
+        <v>8.370198081488454</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368004484549814</v>
+        <v>8.368005824340159</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394445538179951</v>
+        <v>8.394442836208036</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410737886825959</v>
+        <v>8.410736571287831</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.42420033117754</v>
+        <v>8.424200405500361</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428458986682077</v>
+        <v>8.428460278660323</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427260476428875</v>
+        <v>8.427262976066929</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431743443555291</v>
+        <v>8.431747410517165</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.429982956329489</v>
+        <v>8.42999605025023</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439984976434623</v>
+        <v>8.439999278671767</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446523706597301</v>
+        <v>8.446539160201212</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439659240733505</v>
+        <v>8.439674565146053</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419502421219297</v>
+        <v>8.419518939421749</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401932007461012</v>
+        <v>8.401953994505975</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374047501195726</v>
+        <v>8.374066783958627</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336448408015332</v>
+        <v>8.336469579149313</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281293430958559</v>
+        <v>8.281322818811262</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226884103330299</v>
+        <v>8.226915760955878</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173780152219848</v>
+        <v>8.173797081440926</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130608415489021</v>
+        <v>8.130619012814551</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133176064771019</v>
+        <v>8.133173212550867</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185379760998575</v>
+        <v>8.185365895198721</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216304819469821</v>
+        <v>8.216261548153565</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200248845253428</v>
+        <v>8.20019389195634</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171481127704689</v>
+        <v>8.171421396561868</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126939892487023</v>
+        <v>8.126883515761977</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104062792591172</v>
+        <v>8.104016414890593</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.115003920233168</v>
+        <v>8.114968265571632</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164062236398816</v>
+        <v>8.164061045295259</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192485325291168</v>
+        <v>8.192494859845523</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173510983528109</v>
+        <v>8.173531311392862</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198454907861262</v>
+        <v>8.198506727768219</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.202295514503676</v>
+        <v>8.202397179874179</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.233979544145274</v>
+        <v>8.234099273097712</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.325161103649714</v>
+        <v>8.325319472820848</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.282574220964081</v>
+        <v>8.282661081303056</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.284715202398781</v>
+        <v>8.28483525858182</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.268145272234905</v>
+        <v>8.268260066610376</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.279124324597383</v>
+        <v>8.279257688446961</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.314644428644435</v>
+        <v>8.314814548220179</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.335745332306209</v>
+        <v>8.335932559987143</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.242794168477657</v>
+        <v>8.24298781812224</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.152276328872309</v>
+        <v>8.152443727547862</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.058532709122129</v>
+        <v>8.058642420296289</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.013997537306711</v>
+        <v>8.014091335777429</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968778864802783</v>
+        <v>7.968826594135769</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942826473710628</v>
+        <v>7.942858274898665</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949144135841742</v>
+        <v>7.949209194239401</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915627630841225</v>
+        <v>7.91565688743329</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888003985947191</v>
+        <v>7.888016611174042</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873073553991983</v>
+        <v>7.8730957364475</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894267049153208</v>
+        <v>7.894337997030962</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.867064451072565</v>
+        <v>7.86716706563192</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.814079922503673</v>
+        <v>7.814203794993047</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.77363056670608</v>
+        <v>7.773756578501626</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.752801114483841</v>
+        <v>7.752890393832856</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.75009113300624</v>
+        <v>7.750111038023624</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751362510020253</v>
+        <v>7.751322215008056</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.754198047261426</v>
+        <v>7.754072217653832</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.745518317101702</v>
+        <v>7.745293667097624</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.740334632623949</v>
+        <v>7.740056811364559</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.732923247049637</v>
+        <v>7.732593438681018</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.726796991768918</v>
+        <v>7.727031848580267</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.725316478576298</v>
+        <v>7.725401339005618</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.722386279734992</v>
+        <v>7.722179223219579</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.72174161988803</v>
+        <v>7.721224293181433</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.723294940638078</v>
+        <v>7.722307311603188</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.74436009383705</v>
+        <v>7.742524089540508</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.788909990202254</v>
+        <v>7.785594575197562</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.808994104813785</v>
+        <v>7.805039459225478</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.828404101522892</v>
+        <v>7.823645290576628</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.85878175886609</v>
+        <v>7.852362872333819</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.853087203124709</v>
+        <v>7.844791591727077</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.837695456818896</v>
+        <v>7.826480011402266</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,15 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.644097351911792</v>
+        <v>7.650158172052955</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B117">
+        <v>7.667879452642088</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370198081488454</v>
+        <v>8.370196522628667</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368005824340159</v>
+        <v>8.368007137580769</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394442836208036</v>
+        <v>8.394440187682715</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410736571287831</v>
+        <v>8.410735281904271</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424200405500361</v>
+        <v>8.424200478637141</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428460278660323</v>
+        <v>8.428461545513219</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427262976066929</v>
+        <v>8.427265426790909</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431747410517165</v>
+        <v>8.431751299569559</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.42999605025023</v>
+        <v>8.430008885979758</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.439999278671767</v>
+        <v>8.440013300054009</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446539160201212</v>
+        <v>8.446554310399055</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439674565146053</v>
+        <v>8.439689588658268</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419518939421749</v>
+        <v>8.419535134750557</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401953994505975</v>
+        <v>8.401975551096481</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374066783958627</v>
+        <v>8.374085688781296</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336469579149313</v>
+        <v>8.336490338657065</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281322818811262</v>
+        <v>8.281351636854513</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226915760955878</v>
+        <v>8.226946810957545</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173797081440926</v>
+        <v>8.173813685050257</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130619012814551</v>
+        <v>8.130629407221193</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133173212550867</v>
+        <v>8.133170427798055</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185365895198721</v>
+        <v>8.185352311280887</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216261548153565</v>
+        <v>8.216219120537785</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.20019389195634</v>
+        <v>8.200140002057495</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171421396561868</v>
+        <v>8.171362813577138</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126883515761977</v>
+        <v>8.126828211494956</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.104016414890593</v>
+        <v>8.103970902999693</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114968265571632</v>
+        <v>8.114933254750081</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164061045295259</v>
+        <v>8.164059836454625</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192494859845523</v>
+        <v>8.19250419981157</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173531311392862</v>
+        <v>8.173551228270282</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198506727768219</v>
+        <v>8.198557558388083</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.202397179874179</v>
+        <v>8.202496927609076</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.234099273097712</v>
+        <v>8.234216740422294</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.325319472820848</v>
+        <v>8.32547482286612</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.282661081303056</v>
+        <v>8.282746222368031</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.28483525858182</v>
+        <v>8.284952944063797</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.268260066610376</v>
+        <v>8.268372556909737</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.279257688446961</v>
+        <v>8.279388382926907</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.314814548220179</v>
+        <v>8.314981281662103</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.335932559987143</v>
+        <v>8.336116087032337</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.24298781812224</v>
+        <v>8.243177703089708</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.152443727547862</v>
+        <v>8.152607906288509</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.058642420296289</v>
+        <v>8.058750065972429</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.014091335777429</v>
+        <v>8.014183384854743</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968826594135769</v>
+        <v>7.968873439582953</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942858274898665</v>
+        <v>7.942889474069473</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949209194239401</v>
+        <v>7.949273008585267</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.91565688743329</v>
+        <v>7.915685547315275</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888016611174042</v>
+        <v>7.888028923506709</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.8730957364475</v>
+        <v>7.873117402607285</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894337997030962</v>
+        <v>7.894407523202342</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.86716706563192</v>
+        <v>7.867267665610886</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.814203794993047</v>
+        <v>7.81432533056189</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.773756578501626</v>
+        <v>7.773880272896365</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.752890393832856</v>
+        <v>7.752978119361996</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750111038023624</v>
+        <v>7.750130775746522</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751322215008056</v>
+        <v>7.751282861659417</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.754072217653832</v>
+        <v>7.75394892104323</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.745293667097624</v>
+        <v>7.745073174845769</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.740056811364559</v>
+        <v>7.739783821997142</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.732593438681018</v>
+        <v>7.732269115584672</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.727031848580267</v>
+        <v>7.72724028949813</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.725401339005618</v>
+        <v>7.725482295569619</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.722179223219579</v>
+        <v>7.72198826422105</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.721224293181433</v>
+        <v>7.720789842894229</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.722307311603188</v>
+        <v>7.721467583537429</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.742524089540508</v>
+        <v>7.740945493316747</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.785594575197562</v>
+        <v>7.782705364265217</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.805039459225478</v>
+        <v>7.801652816332501</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.823645290576628</v>
+        <v>7.819668324528503</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.852362872333819</v>
+        <v>7.847228213090557</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.844791591727077</v>
+        <v>7.838400307829727</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.826480011402266</v>
+        <v>7.81842698257391</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.650158172052955</v>
+        <v>7.657982942109959</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.667879452642088</v>
+        <v>7.681872176855062</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.72724028949813</v>
+        <v>7.72582161749893</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.725482295569619</v>
+        <v>7.723865291681054</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.72198826422105</v>
+        <v>7.720300789757793</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.720789842894229</v>
+        <v>7.718716643904845</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.721467583537429</v>
+        <v>7.718992969775352</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.740945493316747</v>
+        <v>7.737948711839537</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.782705364265217</v>
+        <v>7.779103184998369</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.801652816332501</v>
+        <v>7.797457279122797</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.819668324528503</v>
+        <v>7.814572557884129</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.847228213090557</v>
+        <v>7.840301025163306</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.838400307829727</v>
+        <v>7.82929007112387</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.81842698257391</v>
+        <v>7.805471602741066</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.657982942109959</v>
+        <v>7.633674798656957</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.681872176855062</v>
+        <v>7.584074338737199</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370196522628667</v>
+        <v>8.370194994035126</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368007137580769</v>
+        <v>8.368008425052938</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394440187682715</v>
+        <v>8.394437591034077</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410735281904271</v>
+        <v>8.410734017903266</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424200478637141</v>
+        <v>8.424200550614636</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428461545513219</v>
+        <v>8.428462787966531</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427265426790909</v>
+        <v>8.427267830022492</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431751299569559</v>
+        <v>8.431755112984998</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430008885979758</v>
+        <v>8.430021471078298</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440013300054009</v>
+        <v>8.440027048772487</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446554310399055</v>
+        <v>8.446569166037971</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439689588658268</v>
+        <v>8.439704320045097</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419535134750557</v>
+        <v>8.419551016578186</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401975551096481</v>
+        <v>8.401996689747198</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374085688781296</v>
+        <v>8.374104226663732</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336490338657065</v>
+        <v>8.336510698423607</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281351636854513</v>
+        <v>8.28137990149348</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226946810957545</v>
+        <v>8.226977270646096</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173813685050257</v>
+        <v>8.17382997234539</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130629407221193</v>
+        <v>8.130639604478109</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133170427798055</v>
+        <v>8.133167708218423</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185352311280887</v>
+        <v>8.185339000756727</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216219120537785</v>
+        <v>8.216177512205078</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200140002057495</v>
+        <v>8.200087145021834</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171362813577138</v>
+        <v>8.171305346009067</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126828211494956</v>
+        <v>8.126773949434869</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103970902999693</v>
+        <v>8.103926232984186</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114933254750081</v>
+        <v>8.114898870625634</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164059836454625</v>
+        <v>8.164058611560346</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.19250419981157</v>
+        <v>8.192513351038301</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173551228270282</v>
+        <v>8.173570746442056</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198557558388083</v>
+        <v>8.198607427697562</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.202496927609076</v>
+        <v>8.202594811339747</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.234216740422294</v>
+        <v>8.234332009463399</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.32547482286612</v>
+        <v>8.325627239164039</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.282746222368031</v>
+        <v>8.282829694672174</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.284952944063797</v>
+        <v>8.285068328314209</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.268372556909737</v>
+        <v>8.268482811681787</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.279388382926907</v>
+        <v>8.279516487241317</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.314981281662103</v>
+        <v>8.315144728879302</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.336116087032337</v>
+        <v>8.336296021921367</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.243177703089708</v>
+        <v>8.243363931928222</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.152607906288509</v>
+        <v>8.152768956917804</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.058750065972429</v>
+        <v>8.05885570375445</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.014183384854743</v>
+        <v>8.014273732868865</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968873439582953</v>
+        <v>7.968919425414837</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942889474069473</v>
+        <v>7.942920088161976</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949273008585267</v>
+        <v>7.949335614204677</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915685547315275</v>
+        <v>7.91571362852013</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888028923506709</v>
+        <v>7.888040933900703</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873117402607285</v>
+        <v>7.87313856976859</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894407523202342</v>
+        <v>7.894475669872034</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.867267665610886</v>
+        <v>7.867366309627306</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.81432533056189</v>
+        <v>7.814444594401119</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.773880272896365</v>
+        <v>7.774001712768152</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.752978119361996</v>
+        <v>7.753064330583905</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750130775746522</v>
+        <v>7.750150344928629</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751282861659417</v>
+        <v>7.751244418951051</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.75394892104323</v>
+        <v>7.753828083142549</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.745073174845769</v>
+        <v>7.744856728269719</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.739783821997142</v>
+        <v>7.73951554375653</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.732269115584672</v>
+        <v>7.731950148734857</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.72582161749893</v>
+        <v>7.724583891568257</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.723865291681054</v>
+        <v>7.722307927220924</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.720300789757793</v>
+        <v>7.718414648748285</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.718716643904845</v>
+        <v>7.716211953682242</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.718992969775352</v>
+        <v>7.715699205051947</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.737948711839537</v>
+        <v>7.733436311501451</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.779103184998369</v>
+        <v>7.772761284823028</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.797457279122797</v>
+        <v>7.79007669414592</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.814572557884129</v>
+        <v>7.805803827866741</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.840301025163306</v>
+        <v>7.828775130833429</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.82929007112387</v>
+        <v>7.814748417048731</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.805471602741066</v>
+        <v>7.786425952973287</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.633674798656957</v>
+        <v>7.619576059277769</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.584074338737199</v>
+        <v>7.552174960924354</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370194994035126</v>
+        <v>8.370193494834869</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368008425052938</v>
+        <v>8.36800968750762</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394437591034077</v>
+        <v>8.394435044753077</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410734017903266</v>
+        <v>8.410732778542874</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424200550614636</v>
+        <v>8.424200621458862</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428462787966531</v>
+        <v>8.428464006718336</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427267830022492</v>
+        <v>8.427270187128798</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431755112984998</v>
+        <v>8.43175885294848</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430021471078298</v>
+        <v>8.430033812813823</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440027048772487</v>
+        <v>8.44004053270292</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446569166037971</v>
+        <v>8.446583735624483</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439704320045097</v>
+        <v>8.439718767743621</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419551016578186</v>
+        <v>8.419566593917912</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.401996689747198</v>
+        <v>8.402017422492476</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374104226663732</v>
+        <v>8.374122408183293</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336510698423607</v>
+        <v>8.33653066988095</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.28137990149348</v>
+        <v>8.281407628509875</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.226977270646096</v>
+        <v>8.227007156681594</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.17382997234539</v>
+        <v>8.173845952273503</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130639604478109</v>
+        <v>8.130649610137962</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133167708218423</v>
+        <v>8.133165051618416</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185339000756727</v>
+        <v>8.185325955474575</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216177512205078</v>
+        <v>8.216136699670493</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200087145021834</v>
+        <v>8.200035291470925</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171305346009067</v>
+        <v>8.171248962347541</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126773949434869</v>
+        <v>8.126720700455335</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103926232984186</v>
+        <v>8.103882381780519</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114898870625634</v>
+        <v>8.114865096652988</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164058611560346</v>
+        <v>8.164057372187438</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192513351038301</v>
+        <v>8.19252231914431</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173570746442056</v>
+        <v>8.173589877707414</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198607427697562</v>
+        <v>8.198656362631571</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.202594811339747</v>
+        <v>8.202690882720676</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.234332009463399</v>
+        <v>8.234445141227013</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.325627239164039</v>
+        <v>8.325776803909232</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.282829694672174</v>
+        <v>8.282911546770272</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.285068328314209</v>
+        <v>8.285181478116982</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.268482811681787</v>
+        <v>8.268590896787689</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.279516487241317</v>
+        <v>8.27964207749692</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.315144728879302</v>
+        <v>8.315304985895866</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.336296021921367</v>
+        <v>8.336472468941057</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.243363931928222</v>
+        <v>8.243546609059297</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.152768956917804</v>
+        <v>8.152926967808217</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.05885570375445</v>
+        <v>8.058959389131021</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.014273732868865</v>
+        <v>8.01436242639206</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968919425414837</v>
+        <v>7.968964575023518</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942920088161976</v>
+        <v>7.942950133485313</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949335614204677</v>
+        <v>7.949397045098804</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.91571362852013</v>
+        <v>7.915741148362907</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888040933900703</v>
+        <v>7.888052652821798</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.87313856976859</v>
+        <v>7.873159254480781</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894475669872034</v>
+        <v>7.894542477594456</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.867366309627306</v>
+        <v>7.867463054051719</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.814444594401119</v>
+        <v>7.814561649311659</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.774001712768152</v>
+        <v>7.774120958758489</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753064330583905</v>
+        <v>7.753149065711256</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750150344928629</v>
+        <v>7.750169744590755</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751244418951051</v>
+        <v>7.751206857159701</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.753828083142549</v>
+        <v>7.753709632490706</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.744856728269719</v>
+        <v>7.744644219197477</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.73951554375653</v>
+        <v>7.739251859700202</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.731950148734857</v>
+        <v>7.731636412846377</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.724583891568257</v>
+        <v>7.72331701687777</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.722307927220924</v>
+        <v>7.720768196674978</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.718414648748285</v>
+        <v>7.716652900369855</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.716211953682242</v>
+        <v>7.714145747895331</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.715699205051947</v>
+        <v>7.713117371516854</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.733436311501451</v>
+        <v>7.730039044819859</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.772761284823028</v>
+        <v>7.768088455069609</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.79007669414592</v>
+        <v>7.78499807150804</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.805803827866741</v>
+        <v>7.800278433257241</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.828775130833429</v>
+        <v>7.822622676541151</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.814748417048731</v>
+        <v>7.807844265415714</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.786425952973287</v>
+        <v>7.778973374814424</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.619576059277769</v>
+        <v>7.625147073575295</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.552174960924354</v>
+        <v>7.564113299066381</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370193494834869</v>
+        <v>8.370192024188192</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.36800968750762</v>
+        <v>8.368010925666862</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394435044753077</v>
+        <v>8.394432547388639</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410732778542874</v>
+        <v>8.410731563109783</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424200621458862</v>
+        <v>8.424200691195136</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428464006718336</v>
+        <v>8.428465202440345</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427270187128798</v>
+        <v>8.427272499424982</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.43175885294848</v>
+        <v>8.431762521561666</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430033812813823</v>
+        <v>8.430045918176063</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.44004053270292</v>
+        <v>8.44005375942066</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446583735624483</v>
+        <v>8.446598027340748</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439718767743621</v>
+        <v>8.439732939869172</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419566593917912</v>
+        <v>8.419581875440871</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402017422492476</v>
+        <v>8.402037760909153</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374122408183293</v>
+        <v>8.374140243514809</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33653066988095</v>
+        <v>8.336550264029441</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281407628509875</v>
+        <v>8.281434833091268</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227007156681594</v>
+        <v>8.227036485103621</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173845952273503</v>
+        <v>8.173861633447736</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130649610137962</v>
+        <v>8.130659429546974</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133165051618416</v>
+        <v>8.133162455899745</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185325955474575</v>
+        <v>8.185313167602942</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216136699670493</v>
+        <v>8.216096660337485</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.200035291470925</v>
+        <v>8.199984413128767</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171248962347541</v>
+        <v>8.171193632256507</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126720700455335</v>
+        <v>8.126668436503032</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103882381780519</v>
+        <v>8.103839327156804</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114865096652988</v>
+        <v>8.114831916858879</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164057372187438</v>
+        <v>8.164056119809652</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.19252231914431</v>
+        <v>8.19253110952895</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173589877707414</v>
+        <v>8.173608633406495</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198656362631571</v>
+        <v>8.198704389131127</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.202690882720676</v>
+        <v>8.202785191519485</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.234445141227013</v>
+        <v>8.234556194487388</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.325776803909232</v>
+        <v>8.325923596259248</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.282911546770272</v>
+        <v>8.282991825352667</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.285181478116982</v>
+        <v>8.285292457698883</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.268590896787689</v>
+        <v>8.268696875531161</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.27964207749692</v>
+        <v>8.27976522685276</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.315304985895866</v>
+        <v>8.315462145037596</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.336472468941057</v>
+        <v>8.336645528385812</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.243546609059297</v>
+        <v>8.24372583497173</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.152926967808217</v>
+        <v>8.153082024041417</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.058959389131021</v>
+        <v>8.059061175571481</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.01436242639206</v>
+        <v>8.014449510317569</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.968964575023518</v>
+        <v>7.969008910961971</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942950133485313</v>
+        <v>7.942979625747856</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949397045098804</v>
+        <v>7.949457334006109</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915741148362907</v>
+        <v>7.915768123476053</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888052652821798</v>
+        <v>7.88806409027248</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873159254480781</v>
+        <v>7.873179472584678</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894542477594456</v>
+        <v>7.894607985353466</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.867463054051719</v>
+        <v>7.867557953113805</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.814561649311659</v>
+        <v>7.814676555812383</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.774120958758489</v>
+        <v>7.774238069370226</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753149065711256</v>
+        <v>7.753232361708323</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750169744590755</v>
+        <v>7.750188973998506</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751206857159701</v>
+        <v>7.751170147796619</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.753709632490706</v>
+        <v>7.753593500321751</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.744644219197477</v>
+        <v>7.74443554319717</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.739251859700202</v>
+        <v>7.73899265656684</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.731636412846377</v>
+        <v>7.731327786254614</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.72331701687777</v>
+        <v>7.722112478613942</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.720768196674978</v>
+        <v>7.719299155860035</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.716652900369855</v>
+        <v>7.71497557492409</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.714145747895331</v>
+        <v>7.712111711384448</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.713117371516854</v>
+        <v>7.710664920828133</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.730039044819859</v>
+        <v>7.726820422897987</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.768088455069609</v>
+        <v>7.763677059685238</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.78499807150804</v>
+        <v>7.780224603025291</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.800278433257241</v>
+        <v>7.795128106410933</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.822622676541151</v>
+        <v>7.81695699604426</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.807844265415714</v>
+        <v>7.801600488264453</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.778973374814424</v>
+        <v>7.772447563978029</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.625147073575295</v>
+        <v>7.629822057756901</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.564113299066381</v>
+        <v>7.571268413285998</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370192024188192</v>
+        <v>8.370190581287073</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368010925666862</v>
+        <v>8.368012140225206</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394432547388639</v>
+        <v>8.394430097544873</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410731563109783</v>
+        <v>8.410730370917943</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424200691195136</v>
+        <v>8.42420075984807</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428465202440345</v>
+        <v>8.42846637577912</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427272499424982</v>
+        <v>8.427274768176677</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431762521561666</v>
+        <v>8.431766120846801</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430045918176063</v>
+        <v>8.430057793889656</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.44005375942066</v>
+        <v>8.440066736214856</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446598027340748</v>
+        <v>8.446612049059857</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439732939869172</v>
+        <v>8.439746844230507</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419581875440871</v>
+        <v>8.41959686949213</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402037760909153</v>
+        <v>8.402057716138094</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374140243514809</v>
+        <v>8.374157742449515</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336550264029441</v>
+        <v>8.336569491457944</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281434833091268</v>
+        <v>8.281461529858774</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227036485103621</v>
+        <v>8.227065271359878</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173861633447736</v>
+        <v>8.173877024162632</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130659429546974</v>
+        <v>8.130669067854424</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133162455899745</v>
+        <v>8.133159919054339</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185313167602942</v>
+        <v>8.185300629614977</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216096660337485</v>
+        <v>8.216057372456325</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199984413128767</v>
+        <v>8.199934482770622</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171193632256507</v>
+        <v>8.171139326519885</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126668436503032</v>
+        <v>8.126617130548826</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103839327156804</v>
+        <v>8.103797047675799</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114831916858879</v>
+        <v>8.114799315817852</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164056119809652</v>
+        <v>8.164054855806175</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.19253110952895</v>
+        <v>8.192539727382862</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173608633406495</v>
+        <v>8.173627024442371</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198704389131127</v>
+        <v>8.198751532188622</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.202785191519485</v>
+        <v>8.202877785702114</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.234556194487388</v>
+        <v>8.234665225887934</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.325923596259248</v>
+        <v>8.326067692473313</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.282991825352667</v>
+        <v>8.283070575333848</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.285292457698883</v>
+        <v>8.285401328850657</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.268696875531161</v>
+        <v>8.268800808781245</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.27976522685276</v>
+        <v>8.279886005661309</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.315462145037596</v>
+        <v>8.315616295108017</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.336645528385812</v>
+        <v>8.336815296746593</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.24372583497173</v>
+        <v>8.243901706404737</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.153082024041417</v>
+        <v>8.153234207559709</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059061175571481</v>
+        <v>8.059161114616536</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.014449510317569</v>
+        <v>8.014535027934315</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969008910961971</v>
+        <v>7.969052454981257</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.942979625747856</v>
+        <v>7.943008580084617</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949457334006109</v>
+        <v>7.949516512460374</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915768123476053</v>
+        <v>7.915794569842659</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.88806409027248</v>
+        <v>7.888075255816727</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873179472584678</v>
+        <v>7.873199239249471</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894607985353466</v>
+        <v>7.894672230637489</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.867557953113805</v>
+        <v>7.867651059002842</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.814676555812383</v>
+        <v>7.814789372242272</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.774238069370226</v>
+        <v>7.774353101060201</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753232361708323</v>
+        <v>7.753314254340201</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750188973998506</v>
+        <v>7.750208032641721</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751170147796619</v>
+        <v>7.751134263545891</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.753593500321751</v>
+        <v>7.753479620441108</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.74443554319717</v>
+        <v>7.744230599420706</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.73899265656684</v>
+        <v>7.738737824640569</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.731327786254614</v>
+        <v>7.731024150799128</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.722112478613942</v>
+        <v>7.721841472266558</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.719299155860035</v>
+        <v>7.717731167055146</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.71497557492409</v>
+        <v>7.71261685459156</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.712111711384448</v>
+        <v>7.709430532188247</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.710664920828133</v>
+        <v>7.70612112514261</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.726820422897987</v>
+        <v>7.720586944272793</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.763677059685238</v>
+        <v>7.755240449059511</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.780224603025291</v>
+        <v>7.770316072140586</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.795128106410933</v>
+        <v>7.783371845388913</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.81695699604426</v>
+        <v>7.802108304641378</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.801600488264453</v>
+        <v>7.781991085820414</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.772447563978029</v>
+        <v>7.747770314674804</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.629822057756901</v>
+        <v>7.603406124547704</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,15 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.571268413285998</v>
+        <v>7.525985664560738</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B118">
+        <v>7.451473164560737</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370190581287073</v>
+        <v>8.370189165353688</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368012140225206</v>
+        <v>8.368013331850968</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394430097544873</v>
+        <v>8.394427693878495</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410730370917943</v>
+        <v>8.410729201307269</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.42420075984807</v>
+        <v>8.424200827441613</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.42846637577912</v>
+        <v>8.428467527357256</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427274768176677</v>
+        <v>8.427276994602298</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431766120846801</v>
+        <v>8.431769652750432</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430057793889656</v>
+        <v>8.430069446426634</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440066736214856</v>
+        <v>8.440079470101846</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446612049059857</v>
+        <v>8.446625808360292</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439746844230507</v>
+        <v>8.439760488344158</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.41959686949213</v>
+        <v>8.419611584105867</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402057716138094</v>
+        <v>8.402077298904512</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374157742449515</v>
+        <v>8.374174914412981</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336569491457944</v>
+        <v>8.336588362362903</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281461529858774</v>
+        <v>8.281487732893209</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227065271359878</v>
+        <v>8.2270935303332</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173877024162632</v>
+        <v>8.173892132408721</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130669067854424</v>
+        <v>8.130678530021624</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133159919054339</v>
+        <v>8.13315743915963</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185300629614977</v>
+        <v>8.185288334273833</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216057372456325</v>
+        <v>8.216018815084823</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199934482770622</v>
+        <v>8.199885474174666</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171139326519885</v>
+        <v>8.171086016990422</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126617130548826</v>
+        <v>8.126566756541546</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103797047675799</v>
+        <v>8.103755522659888</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114799315817852</v>
+        <v>8.1147672786292</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164054855806175</v>
+        <v>8.164053581467801</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192539727382862</v>
+        <v>8.192548177697891</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173627024442371</v>
+        <v>8.173645061301832</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198751532188622</v>
+        <v>8.19879781589068</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.202877785702114</v>
+        <v>8.202968711513428</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.234665225887934</v>
+        <v>8.234772290036705</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.326067692473313</v>
+        <v>8.326209166043565</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283070575333848</v>
+        <v>8.283147839936024</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.285401328850657</v>
+        <v>8.285508151041324</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.268800808781245</v>
+        <v>8.268902755088018</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.279886005661309</v>
+        <v>8.28000448160156</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.315616295108017</v>
+        <v>8.315767521554491</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.336815296746593</v>
+        <v>8.336981866889278</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.243901706404737</v>
+        <v>8.244074316520944</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.153234207559709</v>
+        <v>8.153383597309201</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059161114616536</v>
+        <v>8.059259255964152</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.014535027934315</v>
+        <v>8.014619020997715</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969052454981257</v>
+        <v>7.969095228065759</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943008580084617</v>
+        <v>7.943037011083201</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949516512460374</v>
+        <v>7.949574610845583</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915794569842659</v>
+        <v>7.915820502827789</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888075255816727</v>
+        <v>7.888086158603262</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873199239249471</v>
+        <v>7.873218569007369</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894672230637489</v>
+        <v>7.894735249510398</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.867651059002842</v>
+        <v>7.867742421962578</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.814789372242272</v>
+        <v>7.814900154857197</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.774353101060201</v>
+        <v>7.774466108327175</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753314254340201</v>
+        <v>7.753394778219815</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750208032641721</v>
+        <v>7.750226920215521</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751134263545891</v>
+        <v>7.751099178206324</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.753479620441108</v>
+        <v>7.753367929108441</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.744230599420706</v>
+        <v>7.744029290454995</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.738737824640569</v>
+        <v>7.738487257620678</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.731024150799128</v>
+        <v>7.730725391710869</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.721841472266558</v>
+        <v>7.721574461916711</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.717731167055146</v>
+        <v>7.716152535530746</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.71261685459156</v>
+        <v>7.710271949998217</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.709430532188247</v>
+        <v>7.706777048227607</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.70612112514261</v>
+        <v>7.70167048250584</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.720586944272793</v>
+        <v>7.714505719777994</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.755240449059511</v>
+        <v>7.747048515951628</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.770316072140586</v>
+        <v>7.760716011528565</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.783371845388913</v>
+        <v>7.7720399586275</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.802108304641378</v>
+        <v>7.787928752114415</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.781991085820414</v>
+        <v>7.763506105595471</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.747770314674804</v>
+        <v>7.725013250263452</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.603406124547704</v>
+        <v>7.580129436039993</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.525985664560738</v>
+        <v>7.491842622959156</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.451473164560737</v>
+        <v>7.417330122959156</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370189165353688</v>
+        <v>8.370187775639025</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368013331850968</v>
+        <v>8.368014501187471</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394427693878495</v>
+        <v>8.39442533509636</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410729201307269</v>
+        <v>8.410728053642439</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424200827441613</v>
+        <v>8.424200893999057</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428467527357256</v>
+        <v>8.428468657774463</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427276994602298</v>
+        <v>8.427279179875235</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431769652750432</v>
+        <v>8.431773119146927</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430069446426634</v>
+        <v>8.430080882018135</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440079470101846</v>
+        <v>8.440091967837805</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446625808360292</v>
+        <v>8.446639312539576</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439760488344158</v>
+        <v>8.439773879447964</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419611584105867</v>
+        <v>8.419626027019717</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402077298904512</v>
+        <v>8.402096519537173</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374174914412981</v>
+        <v>8.374191768482008</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336588362362903</v>
+        <v>8.336606886566353</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281487732893209</v>
+        <v>8.281513455759807</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.2270935303332</v>
+        <v>8.227121276367125</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173892132408721</v>
+        <v>8.173906965886308</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130678530021624</v>
+        <v>8.130687820830421</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.13315743915963</v>
+        <v>8.133155014374109</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185288334273833</v>
+        <v>8.185276274618865</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.216018815084823</v>
+        <v>8.215980968051248</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199885474174666</v>
+        <v>8.199837362076281</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171086016990422</v>
+        <v>8.171033676541338</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126566756541546</v>
+        <v>8.126517289364259</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103755522659888</v>
+        <v>8.103714732157833</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.1147672786292</v>
+        <v>8.114735790895082</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164053581467801</v>
+        <v>8.164052298002691</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192548177697891</v>
+        <v>8.192556465276454</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173645061301832</v>
+        <v>8.173662754074975</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19879781589068</v>
+        <v>8.198843263458675</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.202968711513428</v>
+        <v>8.203058013553552</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.234772290036705</v>
+        <v>8.234877439596813</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.326209166043565</v>
+        <v>8.326348087819236</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283147839936024</v>
+        <v>8.283223660768044</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.285508151041324</v>
+        <v>8.28561298152613</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.268902755088018</v>
+        <v>8.269002770791815</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.28000448160156</v>
+        <v>8.280120719804623</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.315767521554491</v>
+        <v>8.315915906625015</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.336981866889278</v>
+        <v>8.337145328223095</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.244074316520944</v>
+        <v>8.244243755069929</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.153383597309201</v>
+        <v>8.15353026937523</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059259255964152</v>
+        <v>8.059355647550914</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.014619020997715</v>
+        <v>8.014701529796728</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969095228065759</v>
+        <v>7.969137250466592</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943037011083201</v>
+        <v>7.943064932808328</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949574610845583</v>
+        <v>7.94963165844783</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915820502827789</v>
+        <v>7.915845937208005</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888086158603262</v>
+        <v>7.888096807387335</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873218569007369</v>
+        <v>7.873237475786181</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894735249510398</v>
+        <v>7.8947970766784</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.867742421962578</v>
+        <v>7.867832090380869</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.814900154857197</v>
+        <v>7.815008957921583</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.774466108327175</v>
+        <v>7.774577143795304</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753394778219815</v>
+        <v>7.753473966852786</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750226920215521</v>
+        <v>7.750245636602837</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751099178206324</v>
+        <v>7.751064866636693</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.753367929108441</v>
+        <v>7.753258364926793</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.744029290454995</v>
+        <v>7.743831522180317</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.738487257620678</v>
+        <v>7.738240852496579</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.730725391710869</v>
+        <v>7.730431397502864</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.721574461916711</v>
+        <v>7.721311367553024</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.716152535530746</v>
+        <v>7.71383727051249</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.710271949998217</v>
+        <v>7.707133068664275</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.706777048227607</v>
+        <v>7.703100278085027</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.70167048250584</v>
+        <v>7.696385137263784</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.714505719777994</v>
+        <v>7.707372708095868</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.747048515951628</v>
+        <v>7.737505303341795</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.760716011528565</v>
+        <v>7.749429730062698</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.7720399586275</v>
+        <v>7.758607565111785</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.787928752114415</v>
+        <v>7.771227988694777</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.763506105595471</v>
+        <v>7.741701918316657</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.725013250263452</v>
+        <v>7.698221156655201</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.580129436039993</v>
+        <v>7.55077405384324</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.491842622959156</v>
+        <v>7.449635208783159</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.417330122959156</v>
+        <v>7.221920863118082</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370187775639025</v>
+        <v>8.370186411421548</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368014501187471</v>
+        <v>8.368015648854202</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.39442533509636</v>
+        <v>8.394423019953155</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410728053642439</v>
+        <v>8.410726927311725</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424200893999057</v>
+        <v>8.424200959543061</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428468657774463</v>
+        <v>8.428469767608625</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427279179875235</v>
+        <v>8.427281325125904</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431773119146927</v>
+        <v>8.431776521841774</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430080882018135</v>
+        <v>8.430092106665526</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440091967837805</v>
+        <v>8.440104235930692</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446639312539576</v>
+        <v>8.446652568627176</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439773879447964</v>
+        <v>8.439787024513878</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419626027019717</v>
+        <v>8.419640205688319</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402096519537173</v>
+        <v>8.40211538798653</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374191768482008</v>
+        <v>8.374208313400601</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336606886566353</v>
+        <v>8.33662507353292</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281513455759807</v>
+        <v>8.28153871153159</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227121276367125</v>
+        <v>8.227148523290079</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173906965886308</v>
+        <v>8.173921532018522</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130687820830421</v>
+        <v>8.130696944891227</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133155014374109</v>
+        <v>8.13315264293319</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185276274618865</v>
+        <v>8.185264443952583</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215980968051248</v>
+        <v>8.215943811919219</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199837362076281</v>
+        <v>8.199790122124817</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.171033676541338</v>
+        <v>8.170982279020546</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126517289364259</v>
+        <v>8.126468704792835</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103714732157833</v>
+        <v>8.103674656913293</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114735790895082</v>
+        <v>8.114704838699682</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164052298002691</v>
+        <v>8.164051006541714</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192556465276454</v>
+        <v>8.192564594740388</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173662754074975</v>
+        <v>8.173680112473736</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198843263458675</v>
+        <v>8.198887897287136</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203058013553552</v>
+        <v>8.203145734850196</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.234877439596813</v>
+        <v>8.234980725372054</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.326348087819236</v>
+        <v>8.32648452612421</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283223660768044</v>
+        <v>8.283298077899936</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.28561298152613</v>
+        <v>8.285715875448522</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269002770791815</v>
+        <v>8.269100910126346</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.280120719804623</v>
+        <v>8.280234782972327</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.315915906625015</v>
+        <v>8.316061529516329</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.337145328223095</v>
+        <v>8.337305766859744</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.244243755069929</v>
+        <v>8.244410108542848</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.15353026937523</v>
+        <v>8.153674297110513</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059355647550914</v>
+        <v>8.059450335629123</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.014701529796728</v>
+        <v>8.014782593217468</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969137250466592</v>
+        <v>7.96917854173328</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943064932808328</v>
+        <v>7.943092358825057</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.94963165844783</v>
+        <v>7.949687683504431</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915845937208005</v>
+        <v>7.915870887199215</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888096807387335</v>
+        <v>7.888107210551203</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873237475786181</v>
+        <v>7.873255972939903</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.8947970766784</v>
+        <v>7.89485774555319</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.867832090380869</v>
+        <v>7.867920110874409</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.815008957921583</v>
+        <v>7.815115833795321</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.774577143795304</v>
+        <v>7.774686258293404</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753473966852786</v>
+        <v>7.753551852680307</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750245636602837</v>
+        <v>7.750264181858302</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.751064866636693</v>
+        <v>7.75103130470409</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.753258364926793</v>
+        <v>7.753150868737551</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.743831522180317</v>
+        <v>7.743637203635426</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.738240852496579</v>
+        <v>7.737998509427804</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.730431397502864</v>
+        <v>7.730142059864366</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.721311367553024</v>
+        <v>7.721052110957082</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.71383727051249</v>
+        <v>7.711625268269866</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.707133068664275</v>
+        <v>7.704305292748336</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.703100278085027</v>
+        <v>7.699504999928932</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.696385137263784</v>
+        <v>7.691332207635834</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.707372708095868</v>
+        <v>7.700492597646952</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.737505303341795</v>
+        <v>7.728337845730051</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.749429730062698</v>
+        <v>7.738643720795863</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.758607565111785</v>
+        <v>7.745888783793637</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.771227988694777</v>
+        <v>7.75556982522369</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.741701918316657</v>
+        <v>7.721497200510422</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.698221156655201</v>
+        <v>7.673865912688188</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.55077405384324</v>
+        <v>7.525256992951892</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.449635208783159</v>
+        <v>7.416588982039671</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.221920863118082</v>
+        <v>7.197634495569211</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.711625268269866</v>
+        <v>7.711736618867782</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.704305292748336</v>
+        <v>7.704426979608469</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.699504999928932</v>
+        <v>7.699662063942721</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.691332207635834</v>
+        <v>7.691519893254916</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.700492597646952</v>
+        <v>7.700699940601703</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.728337845730051</v>
+        <v>7.728586147408429</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.738643720795863</v>
+        <v>7.738938176203657</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.745888783793637</v>
+        <v>7.746253622170807</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.75556982522369</v>
+        <v>7.756023094049628</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.721497200510422</v>
+        <v>7.722111494437798</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.673865912688188</v>
+        <v>7.674666546988858</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.525256992951892</v>
+        <v>7.52644063453764</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.416588982039671</v>
+        <v>7.418582993114128</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.197634495569211</v>
+        <v>7.202211416975183</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370186411421548</v>
+        <v>8.370185072005953</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368015648854202</v>
+        <v>8.368016775447906</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394423019953155</v>
+        <v>8.394420747249207</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410726927311725</v>
+        <v>8.410725821725922</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424200959543061</v>
+        <v>8.424201024095677</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428469767608625</v>
+        <v>8.428470857416777</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427281325125904</v>
+        <v>8.427283431443698</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431776521841774</v>
+        <v>8.43177986257473</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430092106665526</v>
+        <v>8.430103126150893</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440104235930692</v>
+        <v>8.440116280651537</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446652568627176</v>
+        <v>8.446665583396694</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439787024513878</v>
+        <v>8.43979993026006</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419640205688319</v>
+        <v>8.419654127296136</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.40211538798653</v>
+        <v>8.402133913841903</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374208313400601</v>
+        <v>8.374224557595083</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33662507353292</v>
+        <v>8.336642932385949</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.28153871153159</v>
+        <v>8.281563512811484</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227148523290079</v>
+        <v>8.227175284438268</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173921532018522</v>
+        <v>8.173935837963668</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130696944891227</v>
+        <v>8.130705906650631</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.13315264293319</v>
+        <v>8.133150323145273</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185264443952583</v>
+        <v>8.185252835828379</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215943811919219</v>
+        <v>8.215907327954532</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199790122124817</v>
+        <v>8.199743730842679</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170982279020546</v>
+        <v>8.170931799207331</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126468704792835</v>
+        <v>8.126420979456713</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103674656913293</v>
+        <v>8.103635278334938</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114704838699682</v>
+        <v>8.114674408589403</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164051006541714</v>
+        <v>8.164049708143414</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192564594740388</v>
+        <v>8.192572570539308</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173680112473736</v>
+        <v>8.17369714584936</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198887897287136</v>
+        <v>8.198931738980118</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203145734850196</v>
+        <v>8.203231916927196</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.234980725372054</v>
+        <v>8.235082196388094</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.32648452612421</v>
+        <v>8.326618546868389</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283298077899936</v>
+        <v>8.283371129933355</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.285715875448522</v>
+        <v>8.285816885936544</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269100910126346</v>
+        <v>8.269197225316084</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.280234782972327</v>
+        <v>8.280346731489267</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.316061529516329</v>
+        <v>8.316204466513874</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.337305766859744</v>
+        <v>8.337463265763848</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.244410108542848</v>
+        <v>8.244573460318781</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.153674297110513</v>
+        <v>8.153815751256507</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059450335629123</v>
+        <v>8.059543364839891</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.014782593217468</v>
+        <v>8.014862248803549</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.96917854173328</v>
+        <v>7.969219120743811</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943092358825057</v>
+        <v>7.943119302220808</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949687683504431</v>
+        <v>7.949742713250446</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915870887199215</v>
+        <v>7.915895366482989</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888107210551203</v>
+        <v>7.888117376123351</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873255972939903</v>
+        <v>7.873274073277528</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.89485774555319</v>
+        <v>7.894917288311635</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.867920110874409</v>
+        <v>7.868006528368884</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.815115833795321</v>
+        <v>7.815220833016197</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.774686258293404</v>
+        <v>7.774793500930291</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753551852680307</v>
+        <v>7.753628467120085</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750264181858302</v>
+        <v>7.750282556193401</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.75103130470409</v>
+        <v>7.750998469235221</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.753150868737551</v>
+        <v>7.753045383520947</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.743637203635426</v>
+        <v>7.743446246889089</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.737998509427804</v>
+        <v>7.737760131628843</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.730142059864366</v>
+        <v>7.729857273558417</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.721052110957082</v>
+        <v>7.720796615672464</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.711736618867782</v>
+        <v>7.709728556925945</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.704426979608469</v>
+        <v>7.701839311329003</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.699662063942721</v>
+        <v>7.696373956501048</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.691519893254916</v>
+        <v>7.686867467413148</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.700699940601703</v>
+        <v>7.694331656984917</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.728586147408429</v>
+        <v>7.720098461036252</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.738938176203657</v>
+        <v>7.728981005089082</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.746253622170807</v>
+        <v>7.734592100628506</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.756023094049628</v>
+        <v>7.741780074183985</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.722111494437798</v>
+        <v>7.703971047772819</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.674666546988858</v>
+        <v>7.653253250027703</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.52644063453764</v>
+        <v>7.505215164709333</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.418582993114128</v>
+        <v>7.393788188769316</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.202211416975183</v>
+        <v>7.190395948884904</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370185072005953</v>
+        <v>8.370183756722</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368016775447906</v>
+        <v>8.368017881543622</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394420747249207</v>
+        <v>8.3944185158284</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410725821725922</v>
+        <v>8.410724736317322</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201024095677</v>
+        <v>8.424201087678352</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428470857416777</v>
+        <v>8.428471927736028</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427283431443698</v>
+        <v>8.427285499878833</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.43177986257473</v>
+        <v>8.431783143022772</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430103126150893</v>
+        <v>8.430113946046962</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440116280651537</v>
+        <v>8.44012810804513</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446665583396694</v>
+        <v>8.446678363377403</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.43979993026006</v>
+        <v>8.439812603162313</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419654127296136</v>
+        <v>8.419667798769581</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402133913841903</v>
+        <v>8.402152106347687</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374224557595083</v>
+        <v>8.374240509188404</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336642932385949</v>
+        <v>8.336660471922745</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281563512811484</v>
+        <v>8.28158787175326</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227175284438268</v>
+        <v>8.227201572677377</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173935837963668</v>
+        <v>8.173949890626934</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130705906650631</v>
+        <v>8.130714710398614</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133150323145273</v>
+        <v>8.13314805338808</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185252835828379</v>
+        <v>8.185241444038894</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215907327954532</v>
+        <v>8.215871498093762</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199743730842679</v>
+        <v>8.199698165586582</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170931799207331</v>
+        <v>8.170882212771321</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126420979456713</v>
+        <v>8.126374090801693</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103635278334938</v>
+        <v>8.103596578468089</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114674408589403</v>
+        <v>8.114644487554006</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164049708143414</v>
+        <v>8.164048403798652</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192572570539308</v>
+        <v>8.192580396958503</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.17369714584936</v>
+        <v>8.173713863208944</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198931738980118</v>
+        <v>8.198974809385671</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203231916927196</v>
+        <v>8.203316599869497</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235082196388094</v>
+        <v>8.235181899969399</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.326618546868389</v>
+        <v>8.326750213653181</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283371129933355</v>
+        <v>8.283442854068189</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.285816885936544</v>
+        <v>8.285916064194005</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269197225316084</v>
+        <v>8.26929176666831</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.280346731489267</v>
+        <v>8.280456623528698</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.316204466513874</v>
+        <v>8.316344791124145</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.337463265763848</v>
+        <v>8.337617904895229</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.244573460318781</v>
+        <v>8.244733890803241</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.153815751256507</v>
+        <v>8.153954700058346</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059543364839891</v>
+        <v>8.059634778282479</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.014862248803549</v>
+        <v>8.014940532813313</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969219120743811</v>
+        <v>7.969259005733165</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943119302220808</v>
+        <v>7.943145775626185</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949742713250446</v>
+        <v>7.949796773962715</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915895366482989</v>
+        <v>7.915919388231369</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888117376123351</v>
+        <v>7.888127311796545</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873274073277528</v>
+        <v>7.87329178909013</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894917288311635</v>
+        <v>7.894975735952184</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.868006528368884</v>
+        <v>7.8680913861748</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.815220833016197</v>
+        <v>7.815324004378084</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.774793500930291</v>
+        <v>7.774898919166355</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753628467120085</v>
+        <v>7.753703840605492</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750282556193401</v>
+        <v>7.750300759962758</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750998469235221</v>
+        <v>7.750966337970416</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.753045383520947</v>
+        <v>7.752941854301721</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.743446246889089</v>
+        <v>7.743258566917646</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.737760131628843</v>
+        <v>7.737525625258604</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.729857273558417</v>
+        <v>7.729576936322704</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.720796615672464</v>
+        <v>7.720544806972872</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.709728556925945</v>
+        <v>7.708229958937064</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.701839311329003</v>
+        <v>7.699820409249911</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.696373956501048</v>
+        <v>7.693831234687821</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.686867467413148</v>
+        <v>7.683132972600808</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.694331656984917</v>
+        <v>7.689106425417187</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.720098461036252</v>
+        <v>7.713058229239916</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.728981005089082</v>
+        <v>7.720759978647088</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.734592100628506</v>
+        <v>7.72507116726509</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.741780074183985</v>
+        <v>7.730240836346115</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.703971047772819</v>
+        <v>7.689583375974225</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.653253250027703</v>
+        <v>7.636820163664948</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.505215164709333</v>
+        <v>7.490922452561018</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.393788188769316</v>
+        <v>7.380304150390525</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.190395948884904</v>
+        <v>7.195016975668728</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370183756722</v>
+        <v>8.370182464923367</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368017881543622</v>
+        <v>8.368018967695653</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.3944185158284</v>
+        <v>8.39441632457623</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410724736317322</v>
+        <v>8.410723670538729</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201087678352</v>
+        <v>8.424201150311958</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428471927736028</v>
+        <v>8.428472979084464</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427285499878833</v>
+        <v>8.427287531444094</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431783143022772</v>
+        <v>8.431786364802914</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430113946046962</v>
+        <v>8.430124571726477</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.44012810804513</v>
+        <v>8.440139723940128</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446678363377403</v>
+        <v>8.446690914865165</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439812603162313</v>
+        <v>8.439825049464922</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419667798769581</v>
+        <v>8.419681226788505</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402152106347687</v>
+        <v>8.402169974418731</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374240509188404</v>
+        <v>8.374256176013647</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336660471922745</v>
+        <v>8.336677700628982</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.28158787175326</v>
+        <v>8.281611800081343</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227201572677377</v>
+        <v>8.227227400423111</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173949890626934</v>
+        <v>8.173963696671452</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130714710398614</v>
+        <v>8.130723360275358</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.13314805338808</v>
+        <v>8.133145832105196</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185241444038894</v>
+        <v>8.185230262605053</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215871498093762</v>
+        <v>8.215836304914529</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199698165586582</v>
+        <v>8.199653404510872</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170882212771321</v>
+        <v>8.170833496233572</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126374090801693</v>
+        <v>8.126328017054689</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103596578468089</v>
+        <v>8.103558539967803</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114644487554006</v>
+        <v>8.11461506300868</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164048403798652</v>
+        <v>8.164047094434896</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192580396958503</v>
+        <v>8.192588078126402</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173713863208944</v>
+        <v>8.173730273231058</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198974809385671</v>
+        <v>8.19901712862854</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203316599869497</v>
+        <v>8.203399822384839</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235181899969399</v>
+        <v>8.235279881812286</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.326750213653181</v>
+        <v>8.326879587871584</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283442854068189</v>
+        <v>8.283513286165592</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.285916064194005</v>
+        <v>8.286013459586748</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.26929176666831</v>
+        <v>8.269384582660173</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.280456623528698</v>
+        <v>8.280564515152705</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.316344791124145</v>
+        <v>8.316482574199892</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.337617904895229</v>
+        <v>8.337769761343553</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.244733890803241</v>
+        <v>8.244891477559396</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.153954700058346</v>
+        <v>8.154091209373782</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059634778282479</v>
+        <v>8.059724617580098</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.014940532813313</v>
+        <v>8.015017480274217</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969259005733165</v>
+        <v>7.969298214320395</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943145775626185</v>
+        <v>7.943171791234755</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949796773962715</v>
+        <v>7.949849891001628</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915919388231369</v>
+        <v>7.915942965130327</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888127311796545</v>
+        <v>7.888137024944835</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.87329178909013</v>
+        <v>7.873309132176383</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894975735952184</v>
+        <v>7.895033118348215</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.8680913861748</v>
+        <v>7.8681747260593</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.815324004378084</v>
+        <v>7.815425395005166</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.774898919166355</v>
+        <v>7.775002558881654</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753703840605492</v>
+        <v>7.753778002622957</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750300759962758</v>
+        <v>7.750318793651502</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750966337970416</v>
+        <v>7.750934889520222</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.752941854301721</v>
+        <v>7.752840228059677</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.743258566917646</v>
+        <v>7.743074081488333</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.737525625258604</v>
+        <v>7.737294899314339</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.729576936322704</v>
+        <v>7.729300948773662</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.720544806972872</v>
+        <v>7.720296611829558</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.708229958937064</v>
+        <v>7.708052029972774</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.699820409249911</v>
+        <v>7.697959970635015</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.693831234687821</v>
+        <v>7.691535408283804</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.683132972600808</v>
+        <v>7.680283281050359</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.689106425417187</v>
+        <v>7.685177481972744</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.713058229239916</v>
+        <v>7.707764998755916</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.720759978647088</v>
+        <v>7.714669313561375</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.72507116726509</v>
+        <v>7.718082165375255</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.730240836346115</v>
+        <v>7.721702906436321</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.689583375974225</v>
+        <v>7.680225009586703</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.636820163664948</v>
+        <v>7.625579562206326</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.490922452561018</v>
+        <v>7.482987688073079</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.380304150390525</v>
+        <v>7.375447659038503</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,15 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.195016975668728</v>
+        <v>7.208176060803087</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B119">
+        <v>7.234423352127437</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370182464923367</v>
+        <v>8.370181195986623</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368018967695653</v>
+        <v>8.368020034438501</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.39441632457623</v>
+        <v>8.394414172417948</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410723670538729</v>
+        <v>8.410722623862556</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201150311958</v>
+        <v>8.424201212016811</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428472979084464</v>
+        <v>8.428474011961962</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427287531444094</v>
+        <v>8.427289527116487</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431786364802914</v>
+        <v>8.431789529474857</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430124571726477</v>
+        <v>8.430135008371106</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440139723940128</v>
+        <v>8.440151133958629</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446690914865165</v>
+        <v>8.446703243932756</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439825049464922</v>
+        <v>8.4398372751909</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419681226788505</v>
+        <v>8.419694417797055</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402169974418731</v>
+        <v>8.402187526654897</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374256176013647</v>
+        <v>8.374271565626842</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336677700628982</v>
+        <v>8.336694626692402</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281611800081343</v>
+        <v>8.281635309109609</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227227400423111</v>
+        <v>8.227252779660684</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173963696671452</v>
+        <v>8.173977262528826</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130723360275358</v>
+        <v>8.130731860277752</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133145832105196</v>
+        <v>8.133143657802801</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185230262605053</v>
+        <v>8.185219285765669</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215836304914529</v>
+        <v>8.215801731607321</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199653404510872</v>
+        <v>8.199609426532721</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170833496233572</v>
+        <v>8.170785626929712</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126328017054689</v>
+        <v>8.126282737190246</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103558539967803</v>
+        <v>8.10352114607328</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.11461506300868</v>
+        <v>8.114586122776918</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164047094434896</v>
+        <v>8.164045780920237</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192588078126402</v>
+        <v>8.192595618021651</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173730273231058</v>
+        <v>8.173746384280548</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19901712862854</v>
+        <v>8.19905871614117</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203399822384839</v>
+        <v>8.203481621862249</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235279881812286</v>
+        <v>8.235376186054157</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.326879587871584</v>
+        <v>8.327006728803056</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283513286165592</v>
+        <v>8.283582460807626</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.286013459586748</v>
+        <v>8.286109119724323</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269384582660173</v>
+        <v>8.269475720021024</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.280564515152705</v>
+        <v>8.280670460406979</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.316482574199892</v>
+        <v>8.316617884058621</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.337769761343553</v>
+        <v>8.337918909455819</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.244891477559396</v>
+        <v>8.245046295432369</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.154091209373782</v>
+        <v>8.154225342776488</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059724617580098</v>
+        <v>8.059812922942369</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.015017480274217</v>
+        <v>8.015093125034454</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969298214320395</v>
+        <v>7.969336763534365</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943171791234755</v>
+        <v>7.943197360821788</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949849891001628</v>
+        <v>7.949902088850704</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915942965130327</v>
+        <v>7.915966109401959</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888137024944835</v>
+        <v>7.888146522639529</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873309132176383</v>
+        <v>7.873326113866596</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.895033118348215</v>
+        <v>7.895089464298517</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.8681747260593</v>
+        <v>7.868256588314154</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.815425395005166</v>
+        <v>7.815525050422433</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.775002558881654</v>
+        <v>7.775104464440663</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753778002622957</v>
+        <v>7.753850981747728</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750318793651502</v>
+        <v>7.750336657863589</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750934889520222</v>
+        <v>7.750904103324369</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.752840228059677</v>
+        <v>7.752740453644805</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.743074081488333</v>
+        <v>7.742892711048043</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.737294899314339</v>
+        <v>7.737067865529802</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.729300948773662</v>
+        <v>7.729029214313755</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.720296611829558</v>
+        <v>7.720051958878252</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.708052029972774</v>
+        <v>7.707876149875744</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.697959970635015</v>
+        <v>7.695548783695816</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.691535408283804</v>
+        <v>7.688689915543272</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.680283281050359</v>
+        <v>7.676823008573147</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.685177481972744</v>
+        <v>7.680309448743555</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.707764998755916</v>
+        <v>7.701507660256766</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.714669313561375</v>
+        <v>7.707546044605782</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.718082165375255</v>
+        <v>7.709928034263475</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.721702906436321</v>
+        <v>7.711842021114048</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.680225009586703</v>
+        <v>7.669261742818535</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.625579562206326</v>
+        <v>7.612240206916224</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.482987688073079</v>
+        <v>7.471721929776267</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.375447659038503</v>
+        <v>7.365104558834314</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.208176060803087</v>
+        <v>7.207661358704071</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.234423352127437</v>
+        <v>7.192357246539664</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.695548783695816</v>
+        <v>7.695364675500221</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.688689915543272</v>
+        <v>7.688622027119679</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.676823008573147</v>
+        <v>7.676694353542495</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.680309448743555</v>
+        <v>7.680300700038755</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.701507660256766</v>
+        <v>7.701386694978538</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.707546044605782</v>
+        <v>7.707351388271461</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.709928034263475</v>
+        <v>7.709654245507581</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.711842021114048</v>
+        <v>7.711474253043999</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.669261742818535</v>
+        <v>7.668772425173473</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.612240206916224</v>
+        <v>7.611568349094477</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.471721929776267</v>
+        <v>7.470751531039742</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.365104558834314</v>
+        <v>7.363613664128712</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.207661358704071</v>
+        <v>7.205128975983587</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.192357246539664</v>
+        <v>7.181883281479223</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370181195986623</v>
+        <v>8.370179949310197</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368020034438501</v>
+        <v>8.36802108228774</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394414172417948</v>
+        <v>8.394412058316792</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410722623862556</v>
+        <v>8.410721595779949</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201212016811</v>
+        <v>8.424201272812679</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428474011961962</v>
+        <v>8.428475026850991</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427289527116487</v>
+        <v>8.427291487838801</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431789529474857</v>
+        <v>8.431792638543508</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430135008371106</v>
+        <v>8.430145260979847</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440151133958629</v>
+        <v>8.440162343525243</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446703243932756</v>
+        <v>8.446715356439682</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.4398372751909</v>
+        <v>8.439849286151707</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419694417797055</v>
+        <v>8.419707378013991</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402187526654897</v>
+        <v>8.402204771354825</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374271565626842</v>
+        <v>8.374286685319118</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336694626692402</v>
+        <v>8.336711258015757</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281635309109609</v>
+        <v>8.281658409759187</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227252779660684</v>
+        <v>8.227277721963304</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173977262528826</v>
+        <v>8.173990594409087</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130731860277752</v>
+        <v>8.130740214265519</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133143657802801</v>
+        <v>8.133141529046611</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185219285765669</v>
+        <v>8.18520850796765</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215801731607321</v>
+        <v>8.215767761948801</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199609426532721</v>
+        <v>8.199566211299167</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170785626929712</v>
+        <v>8.170738582974961</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126282737190246</v>
+        <v>8.126238230898796</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.10352114607328</v>
+        <v>8.103484380583581</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114586122776918</v>
+        <v>8.114557655074265</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164045780920237</v>
+        <v>8.164044464067139</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192595618021651</v>
+        <v>8.192603020479808</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173746384280548</v>
+        <v>8.173762204422527</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19905871614117</v>
+        <v>8.199099590693141</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203481621862249</v>
+        <v>8.203562034427655</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235376186054157</v>
+        <v>8.235470855339326</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.327006728803056</v>
+        <v>8.327131693703549</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283582460807626</v>
+        <v>8.283650411353769</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.286109119724323</v>
+        <v>8.286203090537338</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269475720021024</v>
+        <v>8.269565223810378</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.280670460406979</v>
+        <v>8.280774511410524</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.316617884058621</v>
+        <v>8.31675078659481</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.337918909455819</v>
+        <v>8.338065420957088</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.245046295432369</v>
+        <v>8.245198416667119</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.154225342776488</v>
+        <v>8.154357161654048</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059812922942369</v>
+        <v>8.059899733224665</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.015093125034454</v>
+        <v>8.015167499812019</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969336763534365</v>
+        <v>7.969374669838205</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943197360821788</v>
+        <v>7.943222495762053</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949902088850704</v>
+        <v>7.949953391154155</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915966109401959</v>
+        <v>7.91598883282544</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888146522639529</v>
+        <v>7.888155811664237</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873326113866596</v>
+        <v>7.873342745045387</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.895089464298517</v>
+        <v>7.895144801575097</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.868256588314154</v>
+        <v>7.868337011820245</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.815525050422433</v>
+        <v>7.815623014622641</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.775104464440663</v>
+        <v>7.775204678753902</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753850981747728</v>
+        <v>7.753922805678077</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750336657863589</v>
+        <v>7.750354353311041</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750904103324369</v>
+        <v>7.750873959613019</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.752740453644805</v>
+        <v>7.752642481696739</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.742892711048043</v>
+        <v>7.742714378617226</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.737067865529802</v>
+        <v>7.736844438277526</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.729029214313755</v>
+        <v>7.728761639041835</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.720051958878252</v>
+        <v>7.719810778385723</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.707876149875744</v>
+        <v>7.707702293123109</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.695364675500221</v>
+        <v>7.691568077735855</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.688622027119679</v>
+        <v>7.684467307257523</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.676694353542495</v>
+        <v>7.671641898588167</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.680300700038755</v>
+        <v>7.673845324178743</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.701386694978538</v>
+        <v>7.693236867357156</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.707351388271461</v>
+        <v>7.698052989883442</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.709654245507581</v>
+        <v>7.698926834615224</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.711474253043999</v>
+        <v>7.698538827099245</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.668772425173473</v>
+        <v>7.65399375051592</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.611568349094477</v>
+        <v>7.593181602987586</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.470751531039742</v>
+        <v>7.452202119044774</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.363613664128712</v>
+        <v>7.342406649600564</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.205128975983587</v>
+        <v>7.185043722997965</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.181883281479223</v>
+        <v>7.11015897807523</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370179949310197</v>
+        <v>8.370178724313448</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.36802108228774</v>
+        <v>8.368022111740849</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394412058316792</v>
+        <v>8.394409981272338</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410721595779949</v>
+        <v>8.410720585799959</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201272812679</v>
+        <v>8.424201332718805</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428475026850991</v>
+        <v>8.428476024217375</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427291487838801</v>
+        <v>8.427293414521097</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431792638543508</v>
+        <v>8.431795693461364</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430145260979847</v>
+        <v>8.430155334377014</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440162343525243</v>
+        <v>8.440173357875683</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446715356439682</v>
+        <v>8.44672725804144</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439849286151707</v>
+        <v>8.439861087956457</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419707378013991</v>
+        <v>8.419720113442438</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402204771354825</v>
+        <v>8.402221716529025</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374286685319118</v>
+        <v>8.374301542128201</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336711258015757</v>
+        <v>8.336727602229104</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281658409759187</v>
+        <v>8.281681112575351</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227277721963304</v>
+        <v>8.227302238509708</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173990594409087</v>
+        <v>8.174003698310138</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130740214265519</v>
+        <v>8.130748425967042</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133141529046611</v>
+        <v>8.133139444458987</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.18520850796765</v>
+        <v>8.185197923856673</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215767761948801</v>
+        <v>8.215734380276508</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199566211299167</v>
+        <v>8.199523739155843</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170738582974961</v>
+        <v>8.170692343230925</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126238230898796</v>
+        <v>8.126194478556492</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103484380583581</v>
+        <v>8.103448227834511</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114557655074265</v>
+        <v>8.114529648492775</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164044464067139</v>
+        <v>8.164043144635912</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192603020479808</v>
+        <v>8.192610289199674</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173762204422527</v>
+        <v>8.173777741435639</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.199099590693141</v>
+        <v>8.199139770419134</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203562034427655</v>
+        <v>8.203641094996641</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235470855339326</v>
+        <v>8.235563930881483</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.327131693703549</v>
+        <v>8.327254537891028</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283650411353769</v>
+        <v>8.283717169994429</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.286203090537338</v>
+        <v>8.286295416350788</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269565223810378</v>
+        <v>8.269653137491725</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.280774511410524</v>
+        <v>8.280876718440648</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.31675078659481</v>
+        <v>8.316881345386228</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.338065420957088</v>
+        <v>8.338209365064944</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.245198416667119</v>
+        <v>8.245347911020227</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.154357161654048</v>
+        <v>8.154486725300941</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059899733224665</v>
+        <v>8.059985085984476</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.015167499812019</v>
+        <v>8.015240636241355</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969374669838205</v>
+        <v>7.96941194915256</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943222495762053</v>
+        <v>7.943247207046704</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949953391154155</v>
+        <v>7.950003820752523</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.91598883282544</v>
+        <v>7.916011146756892</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888155811664237</v>
+        <v>7.888164898529046</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873342745045387</v>
+        <v>7.873359036173037</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.895144801575097</v>
+        <v>7.895199156968442</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.868337011820245</v>
+        <v>7.868416034108648</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.815623014622641</v>
+        <v>7.81571933012995</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.775204678753902</v>
+        <v>7.775303243336603</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753922805678077</v>
+        <v>7.753993501267999</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750354353311041</v>
+        <v>7.750371880804011</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750873959613019</v>
+        <v>7.750844439370093</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.752642481696739</v>
+        <v>7.752546264568279</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.742714378617226</v>
+        <v>7.742539009688683</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.736844438277526</v>
+        <v>7.736624534474968</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.728761639041835</v>
+        <v>7.728498131666496</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.719810778385723</v>
+        <v>7.719573002216116</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.707702293123109</v>
+        <v>7.707530434142503</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.691568077735855</v>
+        <v>7.68792473499296</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.684467307257523</v>
+        <v>7.680493777786189</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.671641898588167</v>
+        <v>7.666797616153911</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.673845324178743</v>
+        <v>7.66766755221592</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.693236867357156</v>
+        <v>7.685465167555742</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.698052989883442</v>
+        <v>7.689205754992994</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.698926834615224</v>
+        <v>7.688765373958654</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.698538827099245</v>
+        <v>7.686356935737681</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.65399375051592</v>
+        <v>7.640191037213756</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.593181602987586</v>
+        <v>7.576221703687417</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.452202119044774</v>
+        <v>7.435522586157248</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.342406649600564</v>
+        <v>7.324130085321256</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.185043722997965</v>
+        <v>7.169078865445092</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.11015897807523</v>
+        <v>7.074481459882841</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370178724313448</v>
+        <v>8.370177520435746</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368022111740849</v>
+        <v>8.368023123277988</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394409981272338</v>
+        <v>8.394407940318912</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410720585799959</v>
+        <v>8.41071959344877</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201332718805</v>
+        <v>8.424201391753916</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428476024217375</v>
+        <v>8.428477004510979</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427293414521097</v>
+        <v>8.427295308042117</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431795693461364</v>
+        <v>8.431798695630771</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430155334377014</v>
+        <v>8.430165233219791</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440173357875683</v>
+        <v>8.440184182064918</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.44672725804144</v>
+        <v>8.44673895419832</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439861087956457</v>
+        <v>8.439872686020639</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419720113442438</v>
+        <v>8.419732629879162</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402221716529025</v>
+        <v>8.40223836991226</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374301542128201</v>
+        <v>8.37431614284932</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336727602229104</v>
+        <v>8.33674366670146</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281681112575351</v>
+        <v>8.281703427743535</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227302238509708</v>
+        <v>8.227326340100815</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.174003698310138</v>
+        <v>8.17401658002675</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130748425967042</v>
+        <v>8.130756498984912</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133139444458987</v>
+        <v>8.133137402716201</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185197923856673</v>
+        <v>8.185187528268422</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215734380276508</v>
+        <v>8.215701571464825</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199523739155843</v>
+        <v>8.19948199111726</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170692343230925</v>
+        <v>8.170646887274113</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126194478556492</v>
+        <v>8.126151461196571</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103448227834511</v>
+        <v>8.103412672676644</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114529648492775</v>
+        <v>8.114502091986227</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164043144635912</v>
+        <v>8.164041823337964</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192610289199674</v>
+        <v>8.192617427749312</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173777741435639</v>
+        <v>8.173793002824631</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.199139770419134</v>
+        <v>8.199179272845459</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203641094996641</v>
+        <v>8.203718837324626</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235563930881483</v>
+        <v>8.235655452523092</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.327254537891028</v>
+        <v>8.327375314826652</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283717169994429</v>
+        <v>8.2837827678017</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.286295416350788</v>
+        <v>8.286386139953525</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269653137491725</v>
+        <v>8.269739503002478</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.280876718440648</v>
+        <v>8.280977130013483</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.316881345386228</v>
+        <v>8.317009621794721</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.338209365064944</v>
+        <v>8.338350808597969</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.245347911020227</v>
+        <v>8.245494845865979</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.154486725300941</v>
+        <v>8.154614091006858</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059985085984476</v>
+        <v>8.060069017535014</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.015240636241355</v>
+        <v>8.015312564917703</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.96941194915256</v>
+        <v>7.969448616877713</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943247207046704</v>
+        <v>7.943271505299316</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.950003820752523</v>
+        <v>7.950053399716523</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.916011146756892</v>
+        <v>7.91603306214817</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888164898529046</v>
+        <v>7.888173789483892</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873359036173037</v>
+        <v>7.873374997305683</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.895199156968442</v>
+        <v>7.895252556330423</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.868416034108648</v>
+        <v>7.868493691418621</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.81571933012995</v>
+        <v>7.81581403806044</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.775303243336603</v>
+        <v>7.775400198364582</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.753993501267999</v>
+        <v>7.754063094558518</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750371880804011</v>
+        <v>7.750389241241592</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750844439370093</v>
+        <v>7.750815524298591</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.752546264568279</v>
+        <v>7.75245175625273</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.742539009688683</v>
+        <v>7.742366532130987</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.736624534474968</v>
+        <v>7.736408073494443</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.728498131666496</v>
+        <v>7.72823860342235</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.719573002216116</v>
+        <v>7.719338563797214</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.707530434142503</v>
+        <v>7.707360547351259</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.68792473499296</v>
+        <v>7.684428855904423</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.680493777786189</v>
+        <v>7.676693879505458</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.666797616153911</v>
+        <v>7.662149826431938</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.66766755221592</v>
+        <v>7.661757453734401</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.685465167555742</v>
+        <v>7.678018661544549</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.689205754992994</v>
+        <v>7.6807346730371</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.688765373958654</v>
+        <v>7.679063295017031</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.686356935737681</v>
+        <v>7.67478484680562</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.640191037213756</v>
+        <v>7.627181126711807</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.576221703687417</v>
+        <v>7.560422248103028</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.435522586157248</v>
+        <v>7.420317711915222</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.324130085321256</v>
+        <v>7.308064328515556</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.169078865445092</v>
+        <v>7.155899977578013</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.074481459882841</v>
+        <v>7.052845436394983</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370177520435746</v>
+        <v>8.370176337135639</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368023123277988</v>
+        <v>8.368024117362756</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394407940318912</v>
+        <v>8.394405934524103</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.41071959344877</v>
+        <v>8.410718618268952</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201391753916</v>
+        <v>8.424201449936254</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428477004510979</v>
+        <v>8.428477968166412</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427295308042117</v>
+        <v>8.427297169250615</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431798695630771</v>
+        <v>8.431801646406081</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430165233219791</v>
+        <v>8.43017496200541</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440184182064918</v>
+        <v>8.440194820974908</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.44673895419832</v>
+        <v>8.446750450183764</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439872686020639</v>
+        <v>8.439884085574409</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419732629879162</v>
+        <v>8.419744932923356</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.40223836991226</v>
+        <v>8.402254738975305</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.37431614284932</v>
+        <v>8.374330494045566</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.33674366670146</v>
+        <v>8.336759458551875</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281703427743535</v>
+        <v>8.281725365104563</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227326340100815</v>
+        <v>8.22735003717554</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.17401658002675</v>
+        <v>8.17402924515906</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130756498984912</v>
+        <v>8.130764436801186</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133137402716201</v>
+        <v>8.133135402545864</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185187528268422</v>
+        <v>8.185177316220207</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215701571464825</v>
+        <v>8.215669320902187</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.19948199111726</v>
+        <v>8.199440948838639</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170646887274113</v>
+        <v>8.170602195365966</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126151461196571</v>
+        <v>8.126109160482116</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103412672676644</v>
+        <v>8.103377700454427</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114502091986227</v>
+        <v>8.114474974856019</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164041823337964</v>
+        <v>8.164040500838858</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192617427749312</v>
+        <v>8.192624439571718</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173793002824631</v>
+        <v>8.173807995832249</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.199179272845459</v>
+        <v>8.199218114915313</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203718837324626</v>
+        <v>8.203795294054583</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235655452523092</v>
+        <v>8.235745458791824</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.327375314826652</v>
+        <v>8.327494076191931</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.2837827678017</v>
+        <v>8.283847234777465</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.286386139953525</v>
+        <v>8.286475302664215</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269739503002478</v>
+        <v>8.269824360820284</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.280977130013483</v>
+        <v>8.281075792960321</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.317009621794721</v>
+        <v>8.317135675061774</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.338350808597969</v>
+        <v>8.338489816078678</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.245494845865979</v>
+        <v>8.245639286297074</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.154614091006858</v>
+        <v>8.154739314140564</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.060069017535014</v>
+        <v>8.06015156299617</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.015312564917703</v>
+        <v>8.015383315439323</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969448616877713</v>
+        <v>7.96948468791463</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943271505299316</v>
+        <v>7.94329540079114</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.950053399716523</v>
+        <v>7.950102149379202</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.91603306214817</v>
+        <v>7.916054589564661</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888173789483892</v>
+        <v>7.888182490531121</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873374997305683</v>
+        <v>7.873390638114345</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.895252556330423</v>
+        <v>7.89530502461497</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.868493691418621</v>
+        <v>7.868570018752596</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.81581403806044</v>
+        <v>7.815907178179669</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.775400198364582</v>
+        <v>7.775495582727464</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.754063094558518</v>
+        <v>7.754131610807624</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750389241241592</v>
+        <v>7.750406435603365</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750815524298591</v>
+        <v>7.750787196787769</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.75245175625273</v>
+        <v>7.752358912314894</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.742366532130987</v>
+        <v>7.742196876096306</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.736408073494443</v>
+        <v>7.736194977076617</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.72823860342235</v>
+        <v>7.727982967989131</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.719338563797214</v>
+        <v>7.719107398086681</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.707360547351259</v>
+        <v>7.707192607191926</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.684428855904423</v>
+        <v>7.681070286229579</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.676693879505458</v>
+        <v>7.673068712248236</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.662149826431938</v>
+        <v>7.657693820262901</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.661757453734401</v>
+        <v>7.656113113657335</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.678018661544549</v>
+        <v>7.670888064805675</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.6807346730371</v>
+        <v>7.672626484320039</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.679063295017031</v>
+        <v>7.669800357240552</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.67478484680562</v>
+        <v>7.663788565592975</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.627181126711807</v>
+        <v>7.614907932013969</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.560422248103028</v>
+        <v>7.545678761501767</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.420317711915222</v>
+        <v>7.406402693615235</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.308064328515556</v>
+        <v>7.293818748417212</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.155899977578013</v>
+        <v>7.144795083709576</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.052845436394983</v>
+        <v>7.038178720860971</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370176337135639</v>
+        <v>8.37017517389001</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368024117362756</v>
+        <v>8.368025094442906</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394405934524103</v>
+        <v>8.394403962987333</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410718618268952</v>
+        <v>8.410717659818758</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201449936254</v>
+        <v>8.424201507283563</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428477968166412</v>
+        <v>8.428478915603653</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427297169250615</v>
+        <v>8.427298998966627</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431801646406081</v>
+        <v>8.43180454709567</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.43017496200541</v>
+        <v>8.430184525077959</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440194820974908</v>
+        <v>8.44020527932193</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446750450183764</v>
+        <v>8.446761751092282</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439884085574409</v>
+        <v>8.439895291670448</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419744932923356</v>
+        <v>8.419757027984987</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402254738975305</v>
+        <v>8.402270830936125</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374330494045566</v>
+        <v>8.37434460205772</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336759458551875</v>
+        <v>8.336774984659929</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281725365104563</v>
+        <v>8.281746934169083</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.22735003717554</v>
+        <v>8.227373339825828</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.17402924515906</v>
+        <v>8.174041699120696</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130764436801186</v>
+        <v>8.130772242782371</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133135402545864</v>
+        <v>8.133133442724507</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185177316220207</v>
+        <v>8.185167282903091</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215669320902187</v>
+        <v>8.215637614469459</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199440948838639</v>
+        <v>8.199400594589125</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170602195365966</v>
+        <v>8.170558248424452</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126109160482116</v>
+        <v>8.126067558680178</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103377700454427</v>
+        <v>8.103343296986267</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114474974856019</v>
+        <v>8.114448286737691</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164040500838858</v>
+        <v>8.164039177761115</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192624439571718</v>
+        <v>8.192631327990249</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173807995832249</v>
+        <v>8.173822727450549</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.199218114915313</v>
+        <v>8.199256313012759</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203795294054583</v>
+        <v>8.203870496762381</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235745458791824</v>
+        <v>8.235833986954274</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.327494076191931</v>
+        <v>8.327610871962069</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283847234777465</v>
+        <v>8.283910599899073</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.286475302664215</v>
+        <v>8.28656294439388</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269824360820284</v>
+        <v>8.269907750025885</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.281075792960321</v>
+        <v>8.281172752500034</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.317135675061774</v>
+        <v>8.317259562399173</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.338489816078678</v>
+        <v>8.338626449831192</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.245639286297074</v>
+        <v>8.245781295220274</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.154739314140564</v>
+        <v>8.154862448229606</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.06015156299617</v>
+        <v>8.060232756343007</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.015383315439323</v>
+        <v>8.015452916447645</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.96948468791463</v>
+        <v>7.969520176684989</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.94329540079114</v>
+        <v>7.94331890345558</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.950102149379202</v>
+        <v>7.95015009036647</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.916054589564661</v>
+        <v>7.916075739202161</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888182490531121</v>
+        <v>7.8881910074374</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873390638114345</v>
+        <v>7.873405967902929</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.89530502461497</v>
+        <v>7.895356585916655</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.868570018752596</v>
+        <v>7.868645049928427</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.815907178179669</v>
+        <v>7.815998788957433</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.775495582727464</v>
+        <v>7.775589434079406</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.754131610807624</v>
+        <v>7.754199074518946</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750406435603365</v>
+        <v>7.750423464941574</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750787196787769</v>
+        <v>7.750759439882067</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.752358912314894</v>
+        <v>7.75226768982542</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.742196876096306</v>
+        <v>7.742029973932382</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.736194977076617</v>
+        <v>7.735985169247455</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.727982967989131</v>
+        <v>7.72773114141357</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.719107398086681</v>
+        <v>7.718879441538448</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.707192607191926</v>
+        <v>7.707026588164387</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.681070286229579</v>
+        <v>7.681007158133868</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.673068712248236</v>
+        <v>7.669974222543688</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.657693820262901</v>
+        <v>7.654331488828193</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.656113113657335</v>
+        <v>7.652053117206621</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.670888064805675</v>
+        <v>7.665240331356198</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.672626484320039</v>
+        <v>7.666565317699919</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.669800357240552</v>
+        <v>7.663172014288624</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.663788565592975</v>
+        <v>7.656180516587726</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.614907932013969</v>
+        <v>7.606948908806539</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.545678761501767</v>
+        <v>7.537872382206764</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.406402693615235</v>
+        <v>7.40090176558342</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.293818748417212</v>
+        <v>7.291191128562746</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.144795083709576</v>
+        <v>7.149802310123937</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,15 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.038178720860971</v>
+        <v>7.055091898029129</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
+        <v>46395</v>
+      </c>
+      <c r="B120">
+        <v>7.097079516626733</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.654331488828193</v>
+        <v>7.654337486018943</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.652053117206621</v>
+        <v>7.652090419491709</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.665240331356198</v>
+        <v>7.665468590001543</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.666565317699919</v>
+        <v>7.666796544955401</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.663172014288624</v>
+        <v>7.663323990088399</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.656180516587726</v>
+        <v>7.656272307210307</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.606948908806539</v>
+        <v>7.606996296956884</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.537872382206764</v>
+        <v>7.537882251110684</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.40090176558342</v>
+        <v>7.400881778155338</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.291191128562746</v>
+        <v>7.291123788382975</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.149802310123937</v>
+        <v>7.149675379373881</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.055091898029129</v>
+        <v>7.054826482493467</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>7.097079516626733</v>
+        <v>7.0951297777337</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.37017517389001</v>
+        <v>8.370174030193336</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368025094442906</v>
+        <v>8.368026054950988</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394403962987333</v>
+        <v>8.39440202483852</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410717659818758</v>
+        <v>8.410716717671464</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201507283563</v>
+        <v>8.42420156381314</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428478915603653</v>
+        <v>8.428479847228665</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427298998966627</v>
+        <v>8.427300797982682</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.43180454709567</v>
+        <v>8.431807398963885</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430184525077959</v>
+        <v>8.430193926634848</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.44020527932193</v>
+        <v>8.440215561663564</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446761751092282</v>
+        <v>8.446772861846982</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439895291670448</v>
+        <v>8.439906309191423</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419757027984987</v>
+        <v>8.419768920292711</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402270830936125</v>
+        <v>8.40228665277046</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.37434460205772</v>
+        <v>8.374358473013572</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336774984659929</v>
+        <v>8.336790251675721</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281746934169083</v>
+        <v>8.281768144131293</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227373339825828</v>
+        <v>8.227396257810934</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.174041699120696</v>
+        <v>8.17405394714644</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130772242782371</v>
+        <v>8.130779920184183</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133133442724507</v>
+        <v>8.133131522075278</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185167282903091</v>
+        <v>8.185157423674386</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215637614469459</v>
+        <v>8.215606438519361</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199400594589125</v>
+        <v>8.199360911226352</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170558248424452</v>
+        <v>8.170515027997006</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126067558680178</v>
+        <v>8.126026638637155</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103343296986267</v>
+        <v>8.103309448545602</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114448286737691</v>
+        <v>8.11442201758811</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164039177761115</v>
+        <v>8.164037854686876</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192631327990249</v>
+        <v>8.192638096213734</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173822727450549</v>
+        <v>8.173837204431612</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.199256313012759</v>
+        <v>8.19929388298555</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203870496762381</v>
+        <v>8.203944475999984</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235833986954274</v>
+        <v>8.235921073067034</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.327610871962069</v>
+        <v>8.327725750475722</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283910599899073</v>
+        <v>8.283972891162678</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.28656294439388</v>
+        <v>8.286649103705312</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269907750025885</v>
+        <v>8.269989708362804</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.281172752500034</v>
+        <v>8.281268052307789</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.317259562399173</v>
+        <v>8.317381339075098</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.338626449831192</v>
+        <v>8.33876077007397</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.245781295220274</v>
+        <v>8.24592093344728</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.154862448229606</v>
+        <v>8.154983545036091</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.060232756343007</v>
+        <v>8.060312630451911</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.015452916447645</v>
+        <v>8.015521395665527</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969520176684989</v>
+        <v>7.969555097150266</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.94331890345558</v>
+        <v>7.943342022901984</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.95015009036647</v>
+        <v>7.950197242626164</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.916075739202161</v>
+        <v>7.916096520902871</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.8881910074374</v>
+        <v>7.888199345744919</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873405967902929</v>
+        <v>7.87342099562522</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.895356585916655</v>
+        <v>7.895407263507303</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.868645049928427</v>
+        <v>7.868718817628983</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.815998788957433</v>
+        <v>7.816088907619921</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.775589434079406</v>
+        <v>7.775681788887463</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.754199074518946</v>
+        <v>7.754265509469188</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750423464941574</v>
+        <v>7.750440330373896</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750759439882067</v>
+        <v>7.750732237251658</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.75226768982542</v>
+        <v>7.752178047298425</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.742029973932382</v>
+        <v>7.741865760098468</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.735985169247455</v>
+        <v>7.735778576238454</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.72773114141357</v>
+        <v>7.727483042033892</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.718879441538448</v>
+        <v>7.718654632069246</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.707026588164387</v>
+        <v>7.706862464854884</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.681007158133868</v>
+        <v>7.680944023638316</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.669974222543688</v>
+        <v>7.666042891753873</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.654337486018943</v>
+        <v>7.650003632990681</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.652090419491709</v>
+        <v>7.647077531251146</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.665468590001543</v>
+        <v>7.658806456202619</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.666796544955401</v>
+        <v>7.65954116704112</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.663323990088399</v>
+        <v>7.655195265676818</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.656272307210307</v>
+        <v>7.64682744727472</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.606996296956884</v>
+        <v>7.596749387221903</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.537882251110684</v>
+        <v>7.527159441034247</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.400881778155338</v>
+        <v>7.391171923842744</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.291123788382975</v>
+        <v>7.282431017632497</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.149675379373881</v>
+        <v>7.145069452349549</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.054826482493467</v>
+        <v>7.051688730027447</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>7.0951297777337</v>
+        <v>7.031817064919304</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370174030193336</v>
+        <v>8.370185072005953</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368026054950988</v>
+        <v>8.368016775447906</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.39440202483852</v>
+        <v>8.394420747249207</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410716717671464</v>
+        <v>8.410725821725922</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.42420156381314</v>
+        <v>8.424201024095677</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428479847228665</v>
+        <v>8.428470857416777</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427300797982682</v>
+        <v>8.427283431443698</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431807398963885</v>
+        <v>8.43177986257473</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430193926634848</v>
+        <v>8.430103126150893</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440215561663564</v>
+        <v>8.440116280651537</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446772861846982</v>
+        <v>8.446665583396694</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439906309191423</v>
+        <v>8.43979993026006</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419768920292711</v>
+        <v>8.419654127296136</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.40228665277046</v>
+        <v>8.402133913841903</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374358473013572</v>
+        <v>8.374224557595083</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336790251675721</v>
+        <v>8.336642932385949</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281768144131293</v>
+        <v>8.281563512811484</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227396257810934</v>
+        <v>8.227175284438268</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.17405394714644</v>
+        <v>8.173935837963668</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130779920184183</v>
+        <v>8.130705906650631</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133131522075278</v>
+        <v>8.133150323145273</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185157423674386</v>
+        <v>8.185252835828379</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215606438519361</v>
+        <v>8.215907327954532</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199360911226352</v>
+        <v>8.199743730842679</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170515027997006</v>
+        <v>8.170931799207331</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126026638637155</v>
+        <v>8.126420979456713</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103309448545602</v>
+        <v>8.103635278334938</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.11442201758811</v>
+        <v>8.114674408589403</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164037854686876</v>
+        <v>8.164049708143414</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192638096213734</v>
+        <v>8.192572570539308</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173837204431612</v>
+        <v>8.17369714584936</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19929388298555</v>
+        <v>8.198931738980118</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203944475999984</v>
+        <v>8.203231916927196</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235921073067034</v>
+        <v>8.235082196388094</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.327725750475722</v>
+        <v>8.326618546868389</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283972891162678</v>
+        <v>8.283371129933355</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.286649103705312</v>
+        <v>8.285816885936544</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269989708362804</v>
+        <v>8.269197225316084</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.281268052307789</v>
+        <v>8.280346731489267</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.317381339075098</v>
+        <v>8.316204466513874</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.33876077007397</v>
+        <v>8.337463265763848</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.24592093344728</v>
+        <v>8.244573460318781</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.154983545036091</v>
+        <v>8.153815751256507</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.060312630451911</v>
+        <v>8.059543364839891</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.015521395665527</v>
+        <v>8.014862248803549</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969555097150266</v>
+        <v>7.969219120743811</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943342022901984</v>
+        <v>7.943119302220808</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.950197242626164</v>
+        <v>7.949742713250446</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.916096520902871</v>
+        <v>7.915895366482989</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888199345744919</v>
+        <v>7.888117376123351</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.87342099562522</v>
+        <v>7.873274073277528</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.895407263507303</v>
+        <v>7.894917288311635</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.868718817628983</v>
+        <v>7.868006528368884</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.816088907619921</v>
+        <v>7.815220833016197</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.775681788887463</v>
+        <v>7.782650313740545</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.754265509469188</v>
+        <v>7.758935884582328</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750440330373896</v>
+        <v>7.752389567168702</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750732237251658</v>
+        <v>7.749183023634693</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.752178047298425</v>
+        <v>7.748450554387771</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.741865760098468</v>
+        <v>7.735401196872155</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.735778576238454</v>
+        <v>7.723124902710619</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.727483042033892</v>
+        <v>7.715859642610725</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.718654632069246</v>
+        <v>7.711825235803909</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.706862464854884</v>
+        <v>7.701550251264349</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.680944023638316</v>
+        <v>7.678475742443178</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.666042891753873</v>
+        <v>7.646405708283128</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.650003632990681</v>
+        <v>7.624371726495236</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.647077531251146</v>
+        <v>7.614309062437421</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.658806456202619</v>
+        <v>7.617108487200002</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.65954116704112</v>
+        <v>7.615345046564567</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.655195265676818</v>
+        <v>7.617203676721177</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.64682744727472</v>
+        <v>7.610126690291933</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.596749387221903</v>
+        <v>7.554921643547448</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.527159441034247</v>
+        <v>7.483047839613066</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.391171923842744</v>
+        <v>7.419936468225526</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.282431017632497</v>
+        <v>7.298895348011223</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.145069452349549</v>
+        <v>7.183392090757487</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.051688730027447</v>
+        <v>7.057015276488878</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>7.031817064919304</v>
+        <v>6.91936501689967</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370185072005953</v>
+        <v>8.370171799508292</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368016775447906</v>
+        <v>8.368027927909083</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394420747249207</v>
+        <v>8.394398245369276</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410725821725922</v>
+        <v>8.410714880650012</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201024095677</v>
+        <v>8.424201674485985</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428470857416777</v>
+        <v>8.428481664599239</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427283431443698</v>
+        <v>8.427304306954257</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.43177986257473</v>
+        <v>8.431812961084349</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430103126150893</v>
+        <v>8.430212261294379</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440116280651537</v>
+        <v>8.440235615806818</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446665583396694</v>
+        <v>8.446794531772847</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.43979993026006</v>
+        <v>8.439927797230974</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419654127296136</v>
+        <v>8.419792116699368</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402133913841903</v>
+        <v>8.402317512811516</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374224557595083</v>
+        <v>8.37438552725542</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336642932385949</v>
+        <v>8.336820033939965</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281563512811484</v>
+        <v>8.281809522021003</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227175284438268</v>
+        <v>8.227440977240036</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173935837963668</v>
+        <v>8.174077845478866</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130705906650631</v>
+        <v>8.130794901745503</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133150323145273</v>
+        <v>8.133127793806011</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185252835828379</v>
+        <v>8.185138209700398</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215907327954532</v>
+        <v>8.215545625720981</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199743730842679</v>
+        <v>8.199283491389984</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170931799207331</v>
+        <v>8.170430695868388</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126420979456713</v>
+        <v>8.125946777970698</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103635278334938</v>
+        <v>8.10324336400811</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114674408589403</v>
+        <v>8.114370697556108</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164049708143414</v>
+        <v>8.164035210690287</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192572570539308</v>
+        <v>8.192651284367184</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.17369714584936</v>
+        <v>8.173865420350992</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198931738980118</v>
+        <v>8.199367199395862</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203231916927196</v>
+        <v>8.204088881397466</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235082196388094</v>
+        <v>8.236091057609316</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.326618546868389</v>
+        <v>8.327949941300405</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283371129933355</v>
+        <v>8.284094359439404</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.285816885936544</v>
+        <v>8.286817122919093</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269197225316084</v>
+        <v>8.270149477055476</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.280346731489267</v>
+        <v>8.281453840097637</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.316204466513874</v>
+        <v>8.317618772283385</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.337463265763848</v>
+        <v>8.339022700899974</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.244573460318781</v>
+        <v>8.246193331098356</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.153815751256507</v>
+        <v>8.155219825451535</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059543364839891</v>
+        <v>8.060468547229631</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.014862248803549</v>
+        <v>8.015655095245453</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969219120743811</v>
+        <v>7.969623286818674</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943119302220808</v>
+        <v>7.943387149035798</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949742713250446</v>
+        <v>7.950289257528176</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915895366482989</v>
+        <v>7.916137018184985</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888117376123351</v>
+        <v>7.888215507673009</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873274073277528</v>
+        <v>7.873450179031072</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894917288311635</v>
+        <v>7.895506056735853</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.868006528368884</v>
+        <v>7.868862687941373</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.815220833016197</v>
+        <v>7.81626481158126</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.782650313740545</v>
+        <v>7.775862149079273</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.758935884582328</v>
+        <v>7.75439538471524</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.752389567168702</v>
+        <v>7.75047357427933</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.749183023634693</v>
+        <v>7.750679432460186</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.748450554387771</v>
+        <v>7.752003343052283</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.735401196872155</v>
+        <v>7.741545145336969</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.723124902710619</v>
+        <v>7.735374750177936</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.715859642610725</v>
+        <v>7.726997709237772</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.711825235803909</v>
+        <v>7.718214213150116</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.701550251264349</v>
+        <v>7.706539804321073</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.678475742443178</v>
+        <v>7.680817833499786</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.646405708283128</v>
+        <v>7.659091930817447</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.624371726495236</v>
+        <v>7.64232943210164</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.614309062437421</v>
+        <v>7.638182199688647</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.617108487200002</v>
+        <v>7.646598850222159</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.615345046564567</v>
+        <v>7.646579966937391</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.617203676721177</v>
+        <v>7.640733989572885</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.610126690291933</v>
+        <v>7.630122267757879</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.554921643547448</v>
+        <v>7.578866818353018</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.483047839613066</v>
+        <v>7.508846451722387</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.419936468225526</v>
+        <v>7.375459501226993</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.298895348011223</v>
+        <v>7.269484937378666</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.183392090757487</v>
+        <v>7.140142670601703</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.057015276488878</v>
+        <v>7.051418880103662</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.91936501689967</v>
+        <v>7.010626395879326</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370171799508292</v>
+        <v>8.370183756722</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368027927909083</v>
+        <v>8.368017881543622</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394398245369276</v>
+        <v>8.3944185158284</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410714880650012</v>
+        <v>8.410724736317322</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201674485985</v>
+        <v>8.424201087678352</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428481664599239</v>
+        <v>8.428471927736028</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427304306954257</v>
+        <v>8.427285499878833</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431812961084349</v>
+        <v>8.431783143022772</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430212261294379</v>
+        <v>8.430113946046962</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440235615806818</v>
+        <v>8.44012810804513</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446794531772847</v>
+        <v>8.446678363377403</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439927797230974</v>
+        <v>8.439812603162313</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419792116699368</v>
+        <v>8.419667798769581</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402317512811516</v>
+        <v>8.402152106347687</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.37438552725542</v>
+        <v>8.374240509188404</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336820033939965</v>
+        <v>8.336660471922745</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281809522021003</v>
+        <v>8.28158787175326</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227440977240036</v>
+        <v>8.227201572677377</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.174077845478866</v>
+        <v>8.173949890626934</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130794901745503</v>
+        <v>8.130714710398614</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133127793806011</v>
+        <v>8.13314805338808</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185138209700398</v>
+        <v>8.185241444038894</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215545625720981</v>
+        <v>8.215871498093762</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199283491389984</v>
+        <v>8.199698165586582</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170430695868388</v>
+        <v>8.170882212771321</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.125946777970698</v>
+        <v>8.126374090801693</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.10324336400811</v>
+        <v>8.103596578468089</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114370697556108</v>
+        <v>8.114644487554006</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164035210690287</v>
+        <v>8.164048403798652</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192651284367184</v>
+        <v>8.192580396958503</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173865420350992</v>
+        <v>8.173713863208944</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.199367199395862</v>
+        <v>8.198974809385671</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.204088881397466</v>
+        <v>8.203316599869497</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.236091057609316</v>
+        <v>8.235181899969399</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.327949941300405</v>
+        <v>8.326750213653181</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.284094359439404</v>
+        <v>8.283442854068189</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.286817122919093</v>
+        <v>8.285916064194005</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.270149477055476</v>
+        <v>8.26929176666831</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.281453840097637</v>
+        <v>8.280456623528698</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.317618772283385</v>
+        <v>8.316344791124145</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.339022700899974</v>
+        <v>8.337617904895229</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.246193331098356</v>
+        <v>8.244733890803241</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.155219825451535</v>
+        <v>8.153954700058346</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.060468547229631</v>
+        <v>8.059634778282479</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.015655095245453</v>
+        <v>8.014940532813313</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969623286818674</v>
+        <v>7.969259005733165</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943387149035798</v>
+        <v>7.943145775626185</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.950289257528176</v>
+        <v>7.949796773962715</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.916137018184985</v>
+        <v>7.915919388231369</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888215507673009</v>
+        <v>7.888127311796545</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873450179031072</v>
+        <v>7.87329178909013</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.895506056735853</v>
+        <v>7.894975735952184</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.868862687941373</v>
+        <v>7.8680913861748</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.81626481158126</v>
+        <v>7.815324004378084</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.775862149079273</v>
+        <v>7.782750242181063</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.75439538471524</v>
+        <v>7.759005655313444</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.75047357427933</v>
+        <v>7.75241074529646</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750679432460186</v>
+        <v>7.749163099375505</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.752003343052283</v>
+        <v>7.748366213089025</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.741545145336969</v>
+        <v>7.735233444778997</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.735374750177936</v>
+        <v>7.72290946672994</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.726997709237772</v>
+        <v>7.715593452561415</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.718214213150116</v>
+        <v>7.711579431114604</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.706539804321073</v>
+        <v>7.701367028766001</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.680817833499786</v>
+        <v>7.678370480285809</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.659091930817447</v>
+        <v>7.642533868472003</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.64232943210164</v>
+        <v>7.620167319018987</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.638182199688647</v>
+        <v>7.609640510124259</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.646598850222159</v>
+        <v>7.610425869878418</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.646579966937391</v>
+        <v>7.607649915628857</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.640733989572885</v>
+        <v>7.607667782546992</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.630122267757879</v>
+        <v>7.598736598146604</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.578866818353018</v>
+        <v>7.542593158561492</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.508846451722387</v>
+        <v>7.470297607417415</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.375459501226993</v>
+        <v>7.404375920519843</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.269484937378666</v>
+        <v>7.284161082560557</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.140142670601703</v>
+        <v>7.168647525570488</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.051418880103662</v>
+        <v>7.042080774711397</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>7.010626395879326</v>
+        <v>6.904611571709334</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370183756722</v>
+        <v>8.370170711590362</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368017881543622</v>
+        <v>8.36802884115388</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.3944185158284</v>
+        <v>8.394396402449932</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410724736317322</v>
+        <v>8.410713984991959</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201087678352</v>
+        <v>8.42420172866162</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428471927736028</v>
+        <v>8.428482551091726</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427285499878833</v>
+        <v>8.427306018367275</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431783143022772</v>
+        <v>8.431815673661202</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430113946046962</v>
+        <v>8.430221202112154</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.44012810804513</v>
+        <v>8.440245395988009</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446678363377403</v>
+        <v>8.446805099995773</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439812603162313</v>
+        <v>8.439938276726895</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419667798769581</v>
+        <v>8.419803430415042</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402152106347687</v>
+        <v>8.402332563846839</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374240509188404</v>
+        <v>8.374398721809719</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336660471922745</v>
+        <v>8.336834561424277</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.28158787175326</v>
+        <v>8.281829706868944</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227201572677377</v>
+        <v>8.227462796658124</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173949890626934</v>
+        <v>8.174089505425108</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130714710398614</v>
+        <v>8.130802211902068</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.13314805338808</v>
+        <v>8.133125984046448</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185241444038894</v>
+        <v>8.185128846438765</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215871498093762</v>
+        <v>8.215515963766373</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199698165586582</v>
+        <v>8.199245723362182</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170882212771321</v>
+        <v>8.170389550184197</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126374090801693</v>
+        <v>8.125907805731483</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103596578468089</v>
+        <v>8.103211102575001</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114644487554006</v>
+        <v>8.114345628086319</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164048403798652</v>
+        <v>8.164033890751796</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192580396958503</v>
+        <v>8.192657710184754</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173713863208944</v>
+        <v>8.173879171682643</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.198974809385671</v>
+        <v>8.199402975037597</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203316599869497</v>
+        <v>8.204159363901855</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235181899969399</v>
+        <v>8.236174022528212</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.326750213653181</v>
+        <v>8.328059342687427</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283442854068189</v>
+        <v>8.284153587899151</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.285916064194005</v>
+        <v>8.28689905369969</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.26929176666831</v>
+        <v>8.27022735670773</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.280456623528698</v>
+        <v>8.281544408282414</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.316344791124145</v>
+        <v>8.317734530349359</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.337617904895229</v>
+        <v>8.339150422162927</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.244733890803241</v>
+        <v>8.246326202427143</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.153954700058346</v>
+        <v>8.155335104388858</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059634778282479</v>
+        <v>8.060544650542983</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.014940532813313</v>
+        <v>8.015720366779782</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969259005733165</v>
+        <v>7.969656581803116</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943145775626185</v>
+        <v>7.943409173436482</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949796773962715</v>
+        <v>7.950334156917777</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915919388231369</v>
+        <v>7.916156751815546</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888127311796545</v>
+        <v>7.888223341348009</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.87329178909013</v>
+        <v>7.873464351012037</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.894975735952184</v>
+        <v>7.895554215107885</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.8680913861748</v>
+        <v>7.868932850656809</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.815324004378084</v>
+        <v>7.816350665549626</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.782750242181063</v>
+        <v>7.775950221866255</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.759005655313444</v>
+        <v>7.754458869160921</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.75241074529646</v>
+        <v>7.750489955257542</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.749163099375505</v>
+        <v>7.750653800524245</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.748366213089025</v>
+        <v>7.751918205058524</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.735233444778997</v>
+        <v>7.741388623180336</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.72290946672994</v>
+        <v>7.735177379942527</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.715593452561415</v>
+        <v>7.726760323311663</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.711579431114604</v>
+        <v>7.717998486550664</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.701367028766001</v>
+        <v>7.706381216923588</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.678370480285809</v>
+        <v>7.680754823090622</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.642533868472003</v>
+        <v>7.655415936323512</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.620167319018987</v>
+        <v>7.638262298004727</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.609640510124259</v>
+        <v>7.633602377591302</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.610425869878418</v>
+        <v>7.640330133288728</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.607649915628857</v>
+        <v>7.639921821898342</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.607667782546992</v>
+        <v>7.633311718181679</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.598736598146604</v>
+        <v>7.621577111476162</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.542593158561492</v>
+        <v>7.569678037379833</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.470297607417415</v>
+        <v>7.499335533990977</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.404375920519843</v>
+        <v>7.366964511982199</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.284161082560557</v>
+        <v>7.26191902226941</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.168647525570488</v>
+        <v>7.135441490622271</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.042080774711397</v>
+        <v>7.047077113690035</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.904611571709334</v>
+        <v>6.996834640358071</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.638262298004727</v>
+        <v>7.63825031680964</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.633602377591302</v>
+        <v>7.633604798273639</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.640330133288728</v>
+        <v>7.64069002166505</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.639921821898342</v>
+        <v>7.639946580404531</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.633311718181679</v>
+        <v>7.633351831941009</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.621577111476162</v>
+        <v>7.621630654250622</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.569678037379833</v>
+        <v>7.569741304536478</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.499335533990977</v>
+        <v>7.499409965573741</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.366964511982199</v>
+        <v>7.367073555103319</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.26191902226941</v>
+        <v>7.262057993165088</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.135441490622271</v>
+        <v>7.135619229585577</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.047077113690035</v>
+        <v>7.047341055275233</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.996834640358071</v>
+        <v>6.997389132116255</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370170711590362</v>
+        <v>8.370182464923367</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.36802884115388</v>
+        <v>8.368018967695653</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394396402449932</v>
+        <v>8.39441632457623</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410713984991959</v>
+        <v>8.410723670538729</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.42420172866162</v>
+        <v>8.424201150311958</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428482551091726</v>
+        <v>8.428472979084464</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427306018367275</v>
+        <v>8.427287531444094</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431815673661202</v>
+        <v>8.431786364802914</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430221202112154</v>
+        <v>8.430124571726477</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440245395988009</v>
+        <v>8.440139723940128</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446805099995773</v>
+        <v>8.446690914865165</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439938276726895</v>
+        <v>8.439825049464922</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419803430415042</v>
+        <v>8.419681226788505</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402332563846839</v>
+        <v>8.402169974418731</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374398721809719</v>
+        <v>8.374256176013647</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336834561424277</v>
+        <v>8.336677700628982</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281829706868944</v>
+        <v>8.281611800081343</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227462796658124</v>
+        <v>8.227227400423111</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.174089505425108</v>
+        <v>8.173963696671452</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130802211902068</v>
+        <v>8.130723360275358</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133125984046448</v>
+        <v>8.133145832105196</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185128846438765</v>
+        <v>8.185230262605053</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215515963766373</v>
+        <v>8.215836304914529</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199245723362182</v>
+        <v>8.199653404510872</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170389550184197</v>
+        <v>8.170833496233572</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.125907805731483</v>
+        <v>8.126328017054689</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103211102575001</v>
+        <v>8.103558539967803</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114345628086319</v>
+        <v>8.11461506300868</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164033890751796</v>
+        <v>8.164047094434896</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192657710184754</v>
+        <v>8.192588078126402</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173879171682643</v>
+        <v>8.173730273231058</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.199402975037597</v>
+        <v>8.19901712862854</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.204159363901855</v>
+        <v>8.203399822384839</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.236174022528212</v>
+        <v>8.235279881812286</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.328059342687427</v>
+        <v>8.326879587871584</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.284153587899151</v>
+        <v>8.283513286165592</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.28689905369969</v>
+        <v>8.286013459586748</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.27022735670773</v>
+        <v>8.269384582660173</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.281544408282414</v>
+        <v>8.280564515152705</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.317734530349359</v>
+        <v>8.316482574199892</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.339150422162927</v>
+        <v>8.337769761343553</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.246326202427143</v>
+        <v>8.244891477559396</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.155335104388858</v>
+        <v>8.154091209373782</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.060544650542983</v>
+        <v>8.059724617580098</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.015720366779782</v>
+        <v>8.015017480274217</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969656581803116</v>
+        <v>7.969298214320395</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943409173436482</v>
+        <v>7.943171791234755</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.950334156917777</v>
+        <v>7.949849891001628</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.916156751815546</v>
+        <v>7.915942965130327</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888223341348009</v>
+        <v>7.888137024944835</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873464351012037</v>
+        <v>7.873309132176383</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.895554215107885</v>
+        <v>7.895033118348215</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.868932850656809</v>
+        <v>7.8681747260593</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.816350665549626</v>
+        <v>7.815425395005166</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.775950221866255</v>
+        <v>7.782848479771676</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.754458869160921</v>
+        <v>7.759074310868312</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750489955257542</v>
+        <v>7.752431687788054</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750653800524245</v>
+        <v>7.749143632447917</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.751918205058524</v>
+        <v>7.748283440797263</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.741388623180336</v>
+        <v>7.735068596199905</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.735177379942527</v>
+        <v>7.722697635003334</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.726760323311663</v>
+        <v>7.715331588131903</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.717998486550664</v>
+        <v>7.711337387809637</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.706381216923588</v>
+        <v>7.701186232765695</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.680754823090622</v>
+        <v>7.678266091170901</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.655415936323512</v>
+        <v>7.642526157367326</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.63825031680964</v>
+        <v>7.616232300779309</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.633604798273639</v>
+        <v>7.605567399733473</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.64069002166505</v>
+        <v>7.606318130495868</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.639946580404531</v>
+        <v>7.603217518833016</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.633351831941009</v>
+        <v>7.601500119135768</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.621630654250622</v>
+        <v>7.592921670770309</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.569741304536478</v>
+        <v>7.537202238280303</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.499409965573741</v>
+        <v>7.466071417066647</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.367073555103319</v>
+        <v>7.401431341654218</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.262057993165088</v>
+        <v>7.285165099557901</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.135619229585577</v>
+        <v>7.17522136958473</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.047341055275233</v>
+        <v>7.059049119922294</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,15 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.997389132116255</v>
+        <v>6.949486874086684</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B121">
+        <v>7.025686874086685</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370182464923367</v>
+        <v>8.370169641360974</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.368018967695653</v>
+        <v>8.36802973941731</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.39441632457623</v>
+        <v>8.394394589718473</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410723670538729</v>
+        <v>8.410713104067908</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201150311958</v>
+        <v>8.42420178208428</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428472979084464</v>
+        <v>8.428483423266863</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427287531444094</v>
+        <v>8.427307701997357</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431786364802914</v>
+        <v>8.431818342069141</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430124571726477</v>
+        <v>8.430229996855353</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440139723940128</v>
+        <v>8.440255016934625</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446690914865165</v>
+        <v>8.446815496181003</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439825049464922</v>
+        <v>8.439948585614943</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419681226788505</v>
+        <v>8.419814560623564</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402169974418731</v>
+        <v>8.402347370430649</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374256176013647</v>
+        <v>8.37441170185997</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336677700628982</v>
+        <v>8.336848854304796</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281611800081343</v>
+        <v>8.281849566478492</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227227400423111</v>
+        <v>8.227484267383231</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173963696671452</v>
+        <v>8.174100978727523</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130723360275358</v>
+        <v>8.130809405481372</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133145832105196</v>
+        <v>8.133124209176197</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185230262605053</v>
+        <v>8.185119640220357</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215836304914529</v>
+        <v>8.215486782047257</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199653404510872</v>
+        <v>8.199208563069963</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170833496233572</v>
+        <v>8.170349063002575</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126328017054689</v>
+        <v>8.12586945197814</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103558539967803</v>
+        <v>8.103179345464776</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.11461506300868</v>
+        <v>8.114320940388648</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164047094434896</v>
+        <v>8.164032572788731</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192588078126402</v>
+        <v>8.192664027591039</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173730273231058</v>
+        <v>8.173892693181617</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.19901712862854</v>
+        <v>8.199438181001549</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203399822384839</v>
+        <v>8.204228735697889</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235279881812286</v>
+        <v>8.236255678462314</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.326879587871584</v>
+        <v>8.328167005087384</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283513286165592</v>
+        <v>8.284211845466661</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.286013459586748</v>
+        <v>8.286979643917972</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269384582660173</v>
+        <v>8.270303944183985</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.280564515152705</v>
+        <v>8.281633477255433</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.316482574199892</v>
+        <v>8.317848380965044</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.337769761343553</v>
+        <v>8.339276051430854</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.244891477559396</v>
+        <v>8.246456927021718</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.154091209373782</v>
+        <v>8.155448536827771</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059724617580098</v>
+        <v>8.060619555985371</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.015017480274217</v>
+        <v>8.015784618932894</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969298214320395</v>
+        <v>7.969689360077372</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943171791234755</v>
+        <v>7.943430850068879</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949849891001628</v>
+        <v>7.950378341123216</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.915942965130327</v>
+        <v>7.916176153634275</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888137024944835</v>
+        <v>7.888231016551501</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873309132176383</v>
+        <v>7.873478253549535</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.895033118348215</v>
+        <v>7.895601575298326</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.8681747260593</v>
+        <v>7.869001870187351</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.815425395005166</v>
+        <v>7.816435164829798</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.782848479771676</v>
+        <v>7.776036932997913</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.759074310868312</v>
+        <v>7.754521413192501</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.752431687788054</v>
+        <v>7.750506177329142</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.749143632447917</v>
+        <v>7.750628663264959</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.748283440797263</v>
+        <v>7.751834494373018</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.735068596199905</v>
+        <v>7.741234546752128</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.722697635003334</v>
+        <v>7.734982950020866</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.715331588131903</v>
+        <v>7.726526359428488</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.711337387809637</v>
+        <v>7.717785672666622</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.701186232765695</v>
+        <v>7.706224424937854</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.678266091170901</v>
+        <v>7.680691896922104</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.642526157367326</v>
+        <v>7.655440788598364</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.616232300779309</v>
+        <v>7.634423586171669</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.605567399733473</v>
+        <v>7.629489313058682</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.606318130495868</v>
+        <v>7.636129933424037</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.603217518833016</v>
+        <v>7.63507852647896</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.601500119135768</v>
+        <v>7.628165170801643</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.592921670770309</v>
+        <v>7.615819674933837</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.537202238280303</v>
+        <v>7.564002847511697</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.466071417066647</v>
+        <v>7.494314940180837</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.401431341654218</v>
+        <v>7.36522066262846</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.285165099557901</v>
+        <v>7.26304081811443</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.17522136958473</v>
+        <v>7.142164253003141</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.059049119922294</v>
+        <v>7.060627038650315</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>6.949486874086684</v>
+        <v>7.023785827657674</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>7.025686874086685</v>
+        <v>7.099985827657675</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370169641360974</v>
+        <v>8.370181195986623</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.36802973941731</v>
+        <v>8.368020034438501</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394394589718473</v>
+        <v>8.394414172417948</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410713104067908</v>
+        <v>8.410722623862556</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.42420178208428</v>
+        <v>8.424201212016811</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428483423266863</v>
+        <v>8.428474011961962</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427307701997357</v>
+        <v>8.427289527116487</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431818342069141</v>
+        <v>8.431789529474857</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430229996855353</v>
+        <v>8.430135008371106</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440255016934625</v>
+        <v>8.440151133958629</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446815496181003</v>
+        <v>8.446703243932756</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439948585614943</v>
+        <v>8.4398372751909</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419814560623564</v>
+        <v>8.419694417797055</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402347370430649</v>
+        <v>8.402187526654897</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.37441170185997</v>
+        <v>8.374271565626842</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336848854304796</v>
+        <v>8.336694626692402</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281849566478492</v>
+        <v>8.281635309109609</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227484267383231</v>
+        <v>8.227252779660684</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.174100978727523</v>
+        <v>8.173977262528826</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130809405481372</v>
+        <v>8.130731860277752</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133124209176197</v>
+        <v>8.133143657802801</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.185119640220357</v>
+        <v>8.185219285765669</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215486782047257</v>
+        <v>8.215801731607321</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199208563069963</v>
+        <v>8.199609426532721</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170349063002575</v>
+        <v>8.170785626929712</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.12586945197814</v>
+        <v>8.126282737190246</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103179345464776</v>
+        <v>8.10352114607328</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114320940388648</v>
+        <v>8.114586122776918</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164032572788731</v>
+        <v>8.164045780920237</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192664027591039</v>
+        <v>8.192595618021651</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173892693181617</v>
+        <v>8.173746384280548</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.199438181001549</v>
+        <v>8.19905871614117</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.204228735697889</v>
+        <v>8.203481621862249</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.236255678462314</v>
+        <v>8.235376186054157</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.328167005087384</v>
+        <v>8.327006728803056</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.284211845466661</v>
+        <v>8.283582460807626</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.286979643917972</v>
+        <v>8.286109119724323</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.270303944183985</v>
+        <v>8.269475720021024</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.281633477255433</v>
+        <v>8.280670460406979</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.317848380965044</v>
+        <v>8.316617884058621</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.339276051430854</v>
+        <v>8.337918909455819</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.246456927021718</v>
+        <v>8.245046295432369</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.155448536827771</v>
+        <v>8.154225342776488</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.060619555985371</v>
+        <v>8.059812922942369</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.015784618932894</v>
+        <v>8.015093125034454</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969689360077372</v>
+        <v>7.969336763534365</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943430850068879</v>
+        <v>7.943197360821788</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.950378341123216</v>
+        <v>7.949902088850704</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.916176153634275</v>
+        <v>7.915966109401959</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888231016551501</v>
+        <v>7.888146522639529</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873478253549535</v>
+        <v>7.873326113866596</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.895601575298326</v>
+        <v>7.895089464298517</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.869001870187351</v>
+        <v>7.868256588314154</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.816435164829798</v>
+        <v>7.815525050422433</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.776036932997913</v>
+        <v>7.782945068829634</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.754521413192501</v>
+        <v>7.75914187737536</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.750506177329142</v>
+        <v>7.752452397284522</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.750628663264959</v>
+        <v>7.749124608354142</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.751834494373018</v>
+        <v>7.74820219476889</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.741234546752128</v>
+        <v>7.734906577285486</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.734982950020866</v>
+        <v>7.722489319275454</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.726526359428488</v>
+        <v>7.715073947133712</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.717785672666622</v>
+        <v>7.711099023915933</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.706224424937854</v>
+        <v>7.701007821338655</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.680691896922104</v>
+        <v>7.678162577545028</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.655440788598364</v>
+        <v>7.642517559928425</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.634423586171669</v>
+        <v>7.613139041775358</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.629489313058682</v>
+        <v>7.602444610360618</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.636129933424037</v>
+        <v>7.603342123160602</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.63507852647896</v>
+        <v>7.60025882026881</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.628165170801643</v>
+        <v>7.596652610477463</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.615819674933837</v>
+        <v>7.588875160153997</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.564002847511697</v>
+        <v>7.533805012233739</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.494314940180837</v>
+        <v>7.464077958584962</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.36522066262846</v>
+        <v>7.401031305723382</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.26304081811443</v>
+        <v>7.289093360808844</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.142164253003141</v>
+        <v>7.184987615666099</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.060627038650315</v>
+        <v>7.078953053030464</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>7.023785827657674</v>
+        <v>6.991716398990583</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>7.099985827657675</v>
+        <v>7.067916398990584</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -399,114 +399,962 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3">
-        <v>46304</v>
+        <v>44743</v>
       </c>
       <c r="B2">
-        <v>7.4965</v>
+        <v>7.070763636363637</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3">
-        <v>46311</v>
+        <v>44778</v>
       </c>
       <c r="B3">
-        <v>7.472021852922396</v>
+        <v>7.110923893388716</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3">
-        <v>46318</v>
+        <v>44806</v>
       </c>
       <c r="B4">
-        <v>7.451082270227925</v>
+        <v>7.111774761760929</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3">
-        <v>46325</v>
+        <v>44834</v>
       </c>
       <c r="B5">
-        <v>7.410784089261159</v>
+        <v>7.010396554369961</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3">
-        <v>46332</v>
+        <v>44869</v>
       </c>
       <c r="B6">
-        <v>7.397795193243351</v>
+        <v>7.016172519348739</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3">
-        <v>46339</v>
+        <v>44897</v>
       </c>
       <c r="B7">
-        <v>7.388304896674095</v>
+        <v>6.973940060280817</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3">
-        <v>46346</v>
+        <v>44932</v>
       </c>
       <c r="B8">
-        <v>7.364721483135911</v>
+        <v>7.148816227651394</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3">
-        <v>46353</v>
+        <v>44960</v>
       </c>
       <c r="B9">
-        <v>7.321426228069024</v>
+        <v>7.213930221344848</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3">
-        <v>46360</v>
+        <v>44988</v>
       </c>
       <c r="B10">
-        <v>7.274755268146046</v>
+        <v>7.065937033005428</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3">
-        <v>46367</v>
+        <v>45016</v>
       </c>
       <c r="B11">
-        <v>7.21537361849297</v>
+        <v>7.184698854130553</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3">
-        <v>46374</v>
+        <v>45051</v>
       </c>
       <c r="B12">
-        <v>7.1620238585572</v>
+        <v>7.377180384079086</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3">
-        <v>46381</v>
+        <v>45079</v>
       </c>
       <c r="B13">
-        <v>7.10291652207224</v>
+        <v>7.403503423015879</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3">
-        <v>46388</v>
+        <v>45107</v>
       </c>
       <c r="B14">
-        <v>7.037566374806113</v>
+        <v>7.516487048413765</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3">
+        <v>45142</v>
+      </c>
+      <c r="B15">
+        <v>7.561084072035582</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="3">
+        <v>45170</v>
+      </c>
+      <c r="B16">
+        <v>7.553232308516616</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="3">
+        <v>45205</v>
+      </c>
+      <c r="B17">
+        <v>7.604310559057743</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3">
+        <v>45233</v>
+      </c>
+      <c r="B18">
+        <v>7.730373630209068</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="3">
+        <v>45261</v>
+      </c>
+      <c r="B19">
+        <v>7.697488056571169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="3">
+        <v>45296</v>
+      </c>
+      <c r="B20">
+        <v>7.771791615374219</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="3">
+        <v>45324</v>
+      </c>
+      <c r="B21">
+        <v>7.825030842231284</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="3">
+        <v>45352</v>
+      </c>
+      <c r="B22">
+        <v>7.789912118471987</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="3">
+        <v>45387</v>
+      </c>
+      <c r="B23">
+        <v>7.799477235711559</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="3">
+        <v>45415</v>
+      </c>
+      <c r="B24">
+        <v>7.788303525525222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="3">
+        <v>45443</v>
+      </c>
+      <c r="B25">
+        <v>7.791268015331068</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="3">
+        <v>45478</v>
+      </c>
+      <c r="B26">
+        <v>7.808639345470778</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="3">
+        <v>45506</v>
+      </c>
+      <c r="B27">
+        <v>7.836357341916631</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="3">
+        <v>45541</v>
+      </c>
+      <c r="B28">
+        <v>7.83554675613027</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="3">
+        <v>45569</v>
+      </c>
+      <c r="B29">
+        <v>7.814830083871981</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="3">
+        <v>45597</v>
+      </c>
+      <c r="B30">
+        <v>7.681399822235107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="3">
+        <v>45632</v>
+      </c>
+      <c r="B31">
+        <v>7.639500141143799</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="3">
+        <v>45660</v>
+      </c>
+      <c r="B32">
+        <v>7.561293125152588</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="3">
+        <v>45688</v>
+      </c>
+      <c r="B33">
+        <v>7.543157198283104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="3">
+        <v>45716</v>
+      </c>
+      <c r="B34">
+        <v>7.52430015563965</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="3">
+        <v>45751</v>
+      </c>
+      <c r="B35">
+        <v>7.91059309865735</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="3">
+        <v>45779</v>
+      </c>
+      <c r="B36">
+        <v>8.08442</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="3">
+        <v>45814</v>
+      </c>
+      <c r="B37">
+        <v>8.207800000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="3">
+        <v>45821</v>
+      </c>
+      <c r="B38">
+        <v>8.304682861335793</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="3">
+        <v>45828</v>
+      </c>
+      <c r="B39">
+        <v>8.315692891147688</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="3">
+        <v>45835</v>
+      </c>
+      <c r="B40">
+        <v>8.32790775177318</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="3">
+        <v>45842</v>
+      </c>
+      <c r="B41">
+        <v>8.341427015046722</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="3">
+        <v>45849</v>
+      </c>
+      <c r="B42">
+        <v>8.370179949310197</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="3">
+        <v>45856</v>
+      </c>
+      <c r="B43">
+        <v>8.36802108228774</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="3">
+        <v>45863</v>
+      </c>
+      <c r="B44">
+        <v>8.394412058316792</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="3">
+        <v>45870</v>
+      </c>
+      <c r="B45">
+        <v>8.410721595779949</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3">
+        <v>45877</v>
+      </c>
+      <c r="B46">
+        <v>8.424201272812679</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="3">
+        <v>45884</v>
+      </c>
+      <c r="B47">
+        <v>8.428475026850991</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="3">
+        <v>45891</v>
+      </c>
+      <c r="B48">
+        <v>8.427291487838801</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="3">
+        <v>45898</v>
+      </c>
+      <c r="B49">
+        <v>8.431792638543508</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="3">
+        <v>45905</v>
+      </c>
+      <c r="B50">
+        <v>8.430145260979847</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="3">
+        <v>45912</v>
+      </c>
+      <c r="B51">
+        <v>8.440162343525243</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="3">
+        <v>45919</v>
+      </c>
+      <c r="B52">
+        <v>8.446715356439682</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="3">
+        <v>45926</v>
+      </c>
+      <c r="B53">
+        <v>8.439849286151707</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="3">
+        <v>45933</v>
+      </c>
+      <c r="B54">
+        <v>8.419707378013991</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3">
+        <v>45940</v>
+      </c>
+      <c r="B55">
+        <v>8.402204771354825</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="3">
+        <v>45947</v>
+      </c>
+      <c r="B56">
+        <v>8.374286685319118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="3">
+        <v>45954</v>
+      </c>
+      <c r="B57">
+        <v>8.336711258015757</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="3">
+        <v>45961</v>
+      </c>
+      <c r="B58">
+        <v>8.281658409759187</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="3">
+        <v>45968</v>
+      </c>
+      <c r="B59">
+        <v>8.227277721963304</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="3">
+        <v>45975</v>
+      </c>
+      <c r="B60">
+        <v>8.173990594409087</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="3">
+        <v>45982</v>
+      </c>
+      <c r="B61">
+        <v>8.130740214265519</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="3">
+        <v>45989</v>
+      </c>
+      <c r="B62">
+        <v>8.133141529046611</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="3">
+        <v>45996</v>
+      </c>
+      <c r="B63">
+        <v>8.18520850796765</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="3">
+        <v>46003</v>
+      </c>
+      <c r="B64">
+        <v>8.215767761948801</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="3">
+        <v>46010</v>
+      </c>
+      <c r="B65">
+        <v>8.199566211299167</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="3">
+        <v>46017</v>
+      </c>
+      <c r="B66">
+        <v>8.170738582974961</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="3">
+        <v>46024</v>
+      </c>
+      <c r="B67">
+        <v>8.126238230898796</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="3">
+        <v>46031</v>
+      </c>
+      <c r="B68">
+        <v>8.103484380583581</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="3">
+        <v>46038</v>
+      </c>
+      <c r="B69">
+        <v>8.114557655074265</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B70">
+        <v>8.164044464067139</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3">
+        <v>46052</v>
+      </c>
+      <c r="B71">
+        <v>8.192603020479808</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="3">
+        <v>46059</v>
+      </c>
+      <c r="B72">
+        <v>8.173762204422527</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3">
+        <v>46066</v>
+      </c>
+      <c r="B73">
+        <v>8.199099590693141</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3">
+        <v>46073</v>
+      </c>
+      <c r="B74">
+        <v>8.203562034427655</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B75">
+        <v>8.235470855339326</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B76">
+        <v>8.327131693703549</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3">
+        <v>46094</v>
+      </c>
+      <c r="B77">
+        <v>8.283650411353769</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3">
+        <v>46101</v>
+      </c>
+      <c r="B78">
+        <v>8.286203090537338</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3">
+        <v>46108</v>
+      </c>
+      <c r="B79">
+        <v>8.269565223810378</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3">
+        <v>46115</v>
+      </c>
+      <c r="B80">
+        <v>8.280774511410524</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3">
+        <v>46122</v>
+      </c>
+      <c r="B81">
+        <v>8.31675078659481</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3">
+        <v>46129</v>
+      </c>
+      <c r="B82">
+        <v>8.338065420957088</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3">
+        <v>46136</v>
+      </c>
+      <c r="B83">
+        <v>8.245198416667119</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B84">
+        <v>8.154357161654048</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B85">
+        <v>8.059899733224665</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B86">
+        <v>8.015167499812019</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="3">
+        <v>46164</v>
+      </c>
+      <c r="B87">
+        <v>7.969374669838205</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B88">
+        <v>7.943222495762053</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B89">
+        <v>7.949953391154155</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B90">
+        <v>7.91598883282544</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B91">
+        <v>7.888155811664237</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B92">
+        <v>7.873342745045387</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B93">
+        <v>7.895144801575097</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B94">
+        <v>7.868337011820245</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B95">
+        <v>7.815623014622641</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B96">
+        <v>7.783040050280166</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B97">
+        <v>7.759208380167758</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B98">
+        <v>7.752472876454386</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B99">
+        <v>7.749106013175658</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B100">
+        <v>7.748122433778569</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B101">
+        <v>7.734747316639106</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B102">
+        <v>7.722284434097866</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B103">
+        <v>7.714820430485462</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B104">
+        <v>7.710864259683063</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B105">
+        <v>7.700831753259207</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B106">
+        <v>7.678059940931574</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B107">
+        <v>7.64250812389699</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B108">
+        <v>7.609582298156793</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B109">
+        <v>7.598796947870797</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B110">
+        <v>7.599715840743986</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B111">
+        <v>7.596422706742693</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B112">
+        <v>7.592299973507801</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B113">
+        <v>7.583906060138329</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B114">
+        <v>7.529315741929946</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B115">
+        <v>7.460722507186014</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B116">
+        <v>7.398892562246965</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B117">
+        <v>7.290402499089421</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B118">
+        <v>7.190676543433959</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B119">
+        <v>7.091515693473663</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
         <v>46395</v>
       </c>
-      <c r="B15">
-        <v>6.970594418122751</v>
+      <c r="B120">
+        <v>7.016215758950302</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B121">
+        <v>7.14996596697301</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURCNH_forecast.xlsx
+++ b/public/data/files/EURCNH_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>8.370179949310197</v>
+        <v>8.370178724313448</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>8.36802108228774</v>
+        <v>8.368022111740849</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>8.394412058316792</v>
+        <v>8.394409981272338</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>8.410721595779949</v>
+        <v>8.410720585799959</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>8.424201272812679</v>
+        <v>8.424201332718805</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>8.428475026850991</v>
+        <v>8.428476024217375</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>8.427291487838801</v>
+        <v>8.427293414521097</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>8.431792638543508</v>
+        <v>8.431795693461364</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>8.430145260979847</v>
+        <v>8.430155334377014</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>8.440162343525243</v>
+        <v>8.440173357875683</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>8.446715356439682</v>
+        <v>8.44672725804144</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>8.439849286151707</v>
+        <v>8.439861087956457</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>8.419707378013991</v>
+        <v>8.419720113442438</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>8.402204771354825</v>
+        <v>8.402221716529025</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>8.374286685319118</v>
+        <v>8.374301542128201</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>8.336711258015757</v>
+        <v>8.336727602229104</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>8.281658409759187</v>
+        <v>8.281681112575351</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>8.227277721963304</v>
+        <v>8.227302238509708</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>8.173990594409087</v>
+        <v>8.174003698310138</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>8.130740214265519</v>
+        <v>8.130748425967042</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>8.133141529046611</v>
+        <v>8.133139444458987</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>8.18520850796765</v>
+        <v>8.185197923856673</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>8.215767761948801</v>
+        <v>8.215734380276508</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>8.199566211299167</v>
+        <v>8.199523739155843</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>8.170738582974961</v>
+        <v>8.170692343230925</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>8.126238230898796</v>
+        <v>8.126194478556492</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>8.103484380583581</v>
+        <v>8.103448227834511</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>8.114557655074265</v>
+        <v>8.114529648492775</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>8.164044464067139</v>
+        <v>8.164043144635912</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>8.192603020479808</v>
+        <v>8.192610289199674</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>8.173762204422527</v>
+        <v>8.173777741435639</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>8.199099590693141</v>
+        <v>8.199139770419134</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>8.203562034427655</v>
+        <v>8.203641094996641</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>8.235470855339326</v>
+        <v>8.235563930881483</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>8.327131693703549</v>
+        <v>8.327254537891028</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>8.283650411353769</v>
+        <v>8.283717169994429</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>8.286203090537338</v>
+        <v>8.286295416350788</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>8.269565223810378</v>
+        <v>8.269653137491725</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>8.280774511410524</v>
+        <v>8.280876718440648</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>8.31675078659481</v>
+        <v>8.316881345386228</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>8.338065420957088</v>
+        <v>8.338209365064944</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>8.245198416667119</v>
+        <v>8.245347911020227</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>8.154357161654048</v>
+        <v>8.154486725300941</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>8.059899733224665</v>
+        <v>8.059985085984476</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>8.015167499812019</v>
+        <v>8.015240636241355</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>7.969374669838205</v>
+        <v>7.96941194915256</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>7.943222495762053</v>
+        <v>7.943247207046704</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>7.949953391154155</v>
+        <v>7.950003820752523</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>7.91598883282544</v>
+        <v>7.916011146756892</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>7.888155811664237</v>
+        <v>7.888164898529046</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>7.873342745045387</v>
+        <v>7.873359036173037</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>7.895144801575097</v>
+        <v>7.895199156968442</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>7.868337011820245</v>
+        <v>7.868416034108648</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>7.815623014622641</v>
+        <v>7.81571933012995</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>7.783040050280166</v>
+        <v>7.783133463712893</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>7.759208380167758</v>
+        <v>7.759273843812778</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>7.752472876454386</v>
+        <v>7.752493127987561</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>7.749106013175658</v>
+        <v>7.749087833545476</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>7.748122433778569</v>
+        <v>7.74804411805319</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>7.734747316639106</v>
+        <v>7.734590745217231</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>7.722284434097866</v>
+        <v>7.722082896720623</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>7.714820430485462</v>
+        <v>7.714570942099606</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>7.710864259683063</v>
+        <v>7.710633017515441</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>7.700831753259207</v>
+        <v>7.700657988002418</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>7.678059940931574</v>
+        <v>7.677958182003737</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>7.64250812389699</v>
+        <v>7.642497894614062</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>7.609582298156793</v>
+        <v>7.607035464793606</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>7.598796947870797</v>
+        <v>7.596288488585603</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>7.599715840743986</v>
+        <v>7.59739818480672</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>7.596422706742693</v>
+        <v>7.593986367339916</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>7.592299973507801</v>
+        <v>7.589522236353289</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>7.583906060138329</v>
+        <v>7.580739867260363</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>7.529315741929946</v>
+        <v>7.526881463418635</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>7.460722507186014</v>
+        <v>7.459692871489436</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>7.398892562246965</v>
+        <v>7.399424755260985</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>7.290402499089421</v>
+        <v>7.294821976775149</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>7.190676543433959</v>
+        <v>7.199904415880741</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>7.091515693473663</v>
+        <v>7.108015867788042</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>7.016215758950302</v>
+        <v>7.044388495535152</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>7.14996596697301</v>
+        <v>7.167155326914513</v>
       </c>
     </row>
   </sheetData>
